--- a/public/assets/National Pharmacovigilance Week.xlsx
+++ b/public/assets/National Pharmacovigilance Week.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC30EB8-4173-472B-B969-4D394576E991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAD5662-AB6A-431B-A2C2-E5E120FD8C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="434">
   <si>
     <t>Timestamp</t>
   </si>
@@ -442,6 +442,891 @@
   </si>
   <si>
     <t>Dr. Paridhi Joshi</t>
+  </si>
+  <si>
+    <t>sendhavaaditya88@gmail.com</t>
+  </si>
+  <si>
+    <t>Aaditya Singh Sendhav</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Pharmacy</t>
+  </si>
+  <si>
+    <t>love.rukks@gmail.com</t>
+  </si>
+  <si>
+    <t>Ruqaiya pansemal</t>
+  </si>
+  <si>
+    <t>dr.sakshibhatt@gmail.com</t>
+  </si>
+  <si>
+    <t>Sakshi Bhatt</t>
+  </si>
+  <si>
+    <t>muskansinghal1503@gmail.com</t>
+  </si>
+  <si>
+    <t>Muskan singhal</t>
+  </si>
+  <si>
+    <t>Amaltas</t>
+  </si>
+  <si>
+    <t>drmankashakhan@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Mankasha Khan</t>
+  </si>
+  <si>
+    <t>Amaltas Medical college</t>
+  </si>
+  <si>
+    <t>General Medicine</t>
+  </si>
+  <si>
+    <t>Mbbs intern</t>
+  </si>
+  <si>
+    <t>sonika8u@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Sonika Shrivastava</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Medical sciences</t>
+  </si>
+  <si>
+    <t>abhirajramchandani@gmail.com</t>
+  </si>
+  <si>
+    <t>Prof. Dr. ABHIRAJ RAMCHANDANI</t>
+  </si>
+  <si>
+    <t>Pathology</t>
+  </si>
+  <si>
+    <t>dubesatvik5@gmail.com</t>
+  </si>
+  <si>
+    <t>Satvik Dube</t>
+  </si>
+  <si>
+    <t>Department of Paediatrics</t>
+  </si>
+  <si>
+    <t>Shahnawaz khan</t>
+  </si>
+  <si>
+    <t>skpkhan80@gmail.com</t>
+  </si>
+  <si>
+    <t>AMALTAS MEDICAL COLLEGE, DEWAS</t>
+  </si>
+  <si>
+    <t>PAEDIATRICS</t>
+  </si>
+  <si>
+    <t>nema22@gmail.com</t>
+  </si>
+  <si>
+    <t>Shrikant Nema</t>
+  </si>
+  <si>
+    <t>AIMS Dewas</t>
+  </si>
+  <si>
+    <t>abhi.pithawa@gmail.com</t>
+  </si>
+  <si>
+    <t>Abhilash Kumar Pithawa</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>dearneha19@gmail.com</t>
+  </si>
+  <si>
+    <t>Neha Raikwar</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of medical sciences Dewas</t>
+  </si>
+  <si>
+    <t>MBBS INTERN</t>
+  </si>
+  <si>
+    <t>Dhanshri Patil</t>
+  </si>
+  <si>
+    <t>dhanshripatil499@gmail.com</t>
+  </si>
+  <si>
+    <t>Amaltas medical college</t>
+  </si>
+  <si>
+    <t>umangrathore741@gmail.com</t>
+  </si>
+  <si>
+    <t>Umang Rathore</t>
+  </si>
+  <si>
+    <t>drmittal.hemant@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Hemant Kumar Mittal</t>
+  </si>
+  <si>
+    <t>Amalatas institute of medical sciences, Dewas</t>
+  </si>
+  <si>
+    <t>Medical Oncology</t>
+  </si>
+  <si>
+    <t>bhushan15192@gmail.com</t>
+  </si>
+  <si>
+    <t>Bhushan Bhimrao Patil</t>
+  </si>
+  <si>
+    <t>Community Medicine</t>
+  </si>
+  <si>
+    <t>Shafiakhan</t>
+  </si>
+  <si>
+    <t>01shafiakhan@gamil.com</t>
+  </si>
+  <si>
+    <t>palakpathak66@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Palak Pathak</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Medical science</t>
+  </si>
+  <si>
+    <t>PSYCHIATRY</t>
+  </si>
+  <si>
+    <t>farooqkhanfrk914@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Mohammed Farooq Khan</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Medical Sciences,Dewas</t>
+  </si>
+  <si>
+    <t>Community Medicine Department</t>
+  </si>
+  <si>
+    <t>rameshwarsisodiya3764@gmail.com</t>
+  </si>
+  <si>
+    <t>Rameshwar sisodiya</t>
+  </si>
+  <si>
+    <t>Surgery</t>
+  </si>
+  <si>
+    <t>MBBS UG</t>
+  </si>
+  <si>
+    <t>drayushaggarwal02@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Ayush Aggarwal</t>
+  </si>
+  <si>
+    <t>Amaltas medical university</t>
+  </si>
+  <si>
+    <t>Community medicine</t>
+  </si>
+  <si>
+    <t>mddoctor47@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Manish Dubey</t>
+  </si>
+  <si>
+    <t>Amaltas institute medical sciences</t>
+  </si>
+  <si>
+    <t>anusirathore@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Anusi Rathore</t>
+  </si>
+  <si>
+    <t>Aims</t>
+  </si>
+  <si>
+    <t>Quality executive</t>
+  </si>
+  <si>
+    <t>shahanashah2@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Shahana Shah</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Homoeopathy Hospital and research centre, Dewas</t>
+  </si>
+  <si>
+    <t>Homoeopathy</t>
+  </si>
+  <si>
+    <t>dixitaverma011@gmail.com</t>
+  </si>
+  <si>
+    <t>Dixita verma</t>
+  </si>
+  <si>
+    <t>shanushah1902@gmail.com</t>
+  </si>
+  <si>
+    <t>Afsha sheikh</t>
+  </si>
+  <si>
+    <t>Quality Manager</t>
+  </si>
+  <si>
+    <t>sharma07442501310@gmail.com</t>
+  </si>
+  <si>
+    <t>Shubham</t>
+  </si>
+  <si>
+    <t>deepak.singh3795@gmail.com</t>
+  </si>
+  <si>
+    <t>Deepak Singh</t>
+  </si>
+  <si>
+    <t>Amaltas institute of Medical Sciences</t>
+  </si>
+  <si>
+    <t>Saarah Ansari</t>
+  </si>
+  <si>
+    <t>ahmad_saarah@yahoo.com</t>
+  </si>
+  <si>
+    <t>ishrata143@gmail.com</t>
+  </si>
+  <si>
+    <t>Ishrat khan</t>
+  </si>
+  <si>
+    <t>Amalats institute of medical science</t>
+  </si>
+  <si>
+    <t>bharti.rishika1610@gmail.com</t>
+  </si>
+  <si>
+    <t>Rishika Bharti</t>
+  </si>
+  <si>
+    <t>anitaghodke24@gmail.com</t>
+  </si>
+  <si>
+    <t>Pro.Dr.Anita Sureshrao Ghodke</t>
+  </si>
+  <si>
+    <t>Dravyaguna Vigyan</t>
+  </si>
+  <si>
+    <t>Principal cum Professor</t>
+  </si>
+  <si>
+    <t>sachin.chouhan99989998@gmail.com</t>
+  </si>
+  <si>
+    <t>Sachin Chouhan</t>
+  </si>
+  <si>
+    <t>Amaltas medical College dewas</t>
+  </si>
+  <si>
+    <t>Obs gyne</t>
+  </si>
+  <si>
+    <t>sht84bio@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Shweta Singh</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Homoeopathic Medical College and research centre</t>
+  </si>
+  <si>
+    <t>HOMOEOPATHIC</t>
+  </si>
+  <si>
+    <t>kshitijaa.1997@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Kshitija Shah</t>
+  </si>
+  <si>
+    <t>punitsengar121@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Punit sengar</t>
+  </si>
+  <si>
+    <t>Dr Mamta Gupta</t>
+  </si>
+  <si>
+    <t>guptadrmamta@yahoo.in</t>
+  </si>
+  <si>
+    <t>Amaltas institute of medical sciences, Dewas</t>
+  </si>
+  <si>
+    <t>shilpabais20@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Shilpa Bais</t>
+  </si>
+  <si>
+    <t>Amaltas institute of homoeopathic hospital and research centre</t>
+  </si>
+  <si>
+    <t>Homoeopathic Materia Medica</t>
+  </si>
+  <si>
+    <t>shahanakhan287@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Shahana Khan</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Homeopathy</t>
+  </si>
+  <si>
+    <t>Practice of medicine</t>
+  </si>
+  <si>
+    <t>anjais.jaiswal921@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Ananya Jaiswal</t>
+  </si>
+  <si>
+    <t>Amaltas institute of homoeopathy</t>
+  </si>
+  <si>
+    <t>Department of human physiology and biochemistry</t>
+  </si>
+  <si>
+    <t>profdrmukeshanatomy@gmail.com</t>
+  </si>
+  <si>
+    <t>Prof.Dr Mukesh Agrawal</t>
+  </si>
+  <si>
+    <t>HUMAN ANATOMY</t>
+  </si>
+  <si>
+    <t>patankarvibha13@gmail.com</t>
+  </si>
+  <si>
+    <t>VIBHA PATANKAR</t>
+  </si>
+  <si>
+    <t>Amaltas institute of Homoeopathy</t>
+  </si>
+  <si>
+    <t>Department of Repertory</t>
+  </si>
+  <si>
+    <t>vijaysinghr2222@gmail.com</t>
+  </si>
+  <si>
+    <t>Vijay Singh</t>
+  </si>
+  <si>
+    <t>Respiratory medicine</t>
+  </si>
+  <si>
+    <t>dr.vinaypatidar@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Vinay Patidar</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Homoeopathy Hospital and Research Centre Dewas</t>
+  </si>
+  <si>
+    <t>Practice of Medicine with Essentials of Pharmacology</t>
+  </si>
+  <si>
+    <t>utsavnayak17@gmail.com</t>
+  </si>
+  <si>
+    <t>Utsav Nayak</t>
+  </si>
+  <si>
+    <t>sahilrewa001@gmail.com</t>
+  </si>
+  <si>
+    <t>Sahil Gupta</t>
+  </si>
+  <si>
+    <t>kratikamalviya54476@gmail.com</t>
+  </si>
+  <si>
+    <t>Kratika Malviya</t>
+  </si>
+  <si>
+    <t>mayankraghu28april@gmail.com</t>
+  </si>
+  <si>
+    <t>mayank raghuwanshi</t>
+  </si>
+  <si>
+    <t>Mahak</t>
+  </si>
+  <si>
+    <t>10ag.mahakasharma@gmail.com</t>
+  </si>
+  <si>
+    <t>vyasmahi06@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahi Vyas</t>
+  </si>
+  <si>
+    <t>tinu.shehla@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr Shehla Jaffri</t>
+  </si>
+  <si>
+    <t>Amaltas institute of homeopathy hospital research centre banger dewas mp</t>
+  </si>
+  <si>
+    <t>Homeopathy</t>
+  </si>
+  <si>
+    <t>bobbykachawa6734@gmail.com</t>
+  </si>
+  <si>
+    <t>Yuvraj kachhawa</t>
+  </si>
+  <si>
+    <t>arora.ayushi30@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayushi Arora</t>
+  </si>
+  <si>
+    <t>Amaltas Institute Of Medical Sciences</t>
+  </si>
+  <si>
+    <t>Shreya Negi</t>
+  </si>
+  <si>
+    <t>vaniknw14@gmail.com</t>
+  </si>
+  <si>
+    <t>akshaylamdade1@gmail.com</t>
+  </si>
+  <si>
+    <t>Akshaykumar Pandharinath Lamdade</t>
+  </si>
+  <si>
+    <t>General medicine</t>
+  </si>
+  <si>
+    <t>neha18ani@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Neha Jain</t>
+  </si>
+  <si>
+    <t>Amaltas Institute of Homoeopathy</t>
+  </si>
+  <si>
+    <t>Dept. Of Homoeopathic Materia Medica</t>
+  </si>
+  <si>
+    <t>patidarvanshika99@gmail.com</t>
+  </si>
+  <si>
+    <t>Vanshika surya</t>
+  </si>
+  <si>
+    <t>panjwanikashish0512@gmail.com</t>
+  </si>
+  <si>
+    <t>Kashish panjwani</t>
+  </si>
+  <si>
+    <t>drprashantw@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr prashant</t>
+  </si>
+  <si>
+    <t>Sakshi Dwivedi</t>
+  </si>
+  <si>
+    <t>1234sakshidwivedi@gmail.com</t>
+  </si>
+  <si>
+    <t>Amaltas hospital</t>
+  </si>
+  <si>
+    <t>tusharshembekar12@gmail.com</t>
+  </si>
+  <si>
+    <t>Tushar Shembekar</t>
+  </si>
+  <si>
+    <t>First prof 2026-27</t>
+  </si>
+  <si>
+    <t>kashishmalviya95@gmail.com</t>
+  </si>
+  <si>
+    <t>Kashish Malviya</t>
+  </si>
+  <si>
+    <t>Medical</t>
+  </si>
+  <si>
+    <t>2026 batch</t>
+  </si>
+  <si>
+    <t>soniyadewda6@gmail.com</t>
+  </si>
+  <si>
+    <t>Soniya dewda</t>
+  </si>
+  <si>
+    <t>Amaltas institute of medical science Dewas</t>
+  </si>
+  <si>
+    <t>Mbbs</t>
+  </si>
+  <si>
+    <t>sumedhapande08@gmail.com</t>
+  </si>
+  <si>
+    <t>Sumedha pande</t>
+  </si>
+  <si>
+    <t>sh4485053@gmail.com</t>
+  </si>
+  <si>
+    <t>Alisha Husain</t>
+  </si>
+  <si>
+    <t>MBBS</t>
+  </si>
+  <si>
+    <t>abhishekparmar1256@gmail.com</t>
+  </si>
+  <si>
+    <t>Abhishek Parmar</t>
+  </si>
+  <si>
+    <t>raghavendraraghuwanshi092@gmail.com</t>
+  </si>
+  <si>
+    <t>Raghvendra Raghuwanshi</t>
+  </si>
+  <si>
+    <t>jeetendrarajouriya98@gmail.com</t>
+  </si>
+  <si>
+    <t>Jeetendra Rajouriya</t>
+  </si>
+  <si>
+    <t>Amaltas institute</t>
+  </si>
+  <si>
+    <t>sonumewada540@gmail.com</t>
+  </si>
+  <si>
+    <t>sonu mewada</t>
+  </si>
+  <si>
+    <t>29aditijain@gmail.com</t>
+  </si>
+  <si>
+    <t>Aditi Jain</t>
+  </si>
+  <si>
+    <t>shivamsoni200024@gmail.com</t>
+  </si>
+  <si>
+    <t>Shivam Soni</t>
+  </si>
+  <si>
+    <t>AIMS DEWAS</t>
+  </si>
+  <si>
+    <t>manojtehariya78@gmail.com</t>
+  </si>
+  <si>
+    <t>Akshat sharma</t>
+  </si>
+  <si>
+    <t>anshikakhare41@gmail.com</t>
+  </si>
+  <si>
+    <t>Anshika Khare</t>
+  </si>
+  <si>
+    <t>mr8886357@gmail.com</t>
+  </si>
+  <si>
+    <t>Madhu Rathor</t>
+  </si>
+  <si>
+    <t>Students</t>
+  </si>
+  <si>
+    <t>viiibluejeenalmanloi30@gmail.com</t>
+  </si>
+  <si>
+    <t>Jeenal Mandloi</t>
+  </si>
+  <si>
+    <t>1st year student</t>
+  </si>
+  <si>
+    <t>yashprajapati8590@gmail.com</t>
+  </si>
+  <si>
+    <t>Yash Prajapati</t>
+  </si>
+  <si>
+    <t>ansarp6990@gmail.com</t>
+  </si>
+  <si>
+    <t>Anshika patel</t>
+  </si>
+  <si>
+    <t>Amaltash institute of medical sciences</t>
+  </si>
+  <si>
+    <t>adityanidariya12@gmail.com</t>
+  </si>
+  <si>
+    <t>Aditya Nidariya</t>
+  </si>
+  <si>
+    <t>praadeepdhakad@gmail.com</t>
+  </si>
+  <si>
+    <t>Pradeep dhakad</t>
+  </si>
+  <si>
+    <t>shwetapatidar2007@gmail.com</t>
+  </si>
+  <si>
+    <t>Shweta patidar</t>
+  </si>
+  <si>
+    <t>Manoj Rathor</t>
+  </si>
+  <si>
+    <t>manojrathor10jan2002@gmail.com</t>
+  </si>
+  <si>
+    <t>Aims DEWAS</t>
+  </si>
+  <si>
+    <t>arsejayraj@gmail.com</t>
+  </si>
+  <si>
+    <t>Jayraj Aarse</t>
+  </si>
+  <si>
+    <t>sourabhmukati251@gmail.com</t>
+  </si>
+  <si>
+    <t>Sourabh mukati</t>
+  </si>
+  <si>
+    <t>rashika.choudhary93294@gmail.com</t>
+  </si>
+  <si>
+    <t>Rashika Choudhary</t>
+  </si>
+  <si>
+    <t>tanishkadangi906@gmail.com</t>
+  </si>
+  <si>
+    <t>Tanishka Dangi</t>
+  </si>
+  <si>
+    <t>priyanshugoyalrekhanagar@gmail.com</t>
+  </si>
+  <si>
+    <t>Priyanshu Goyal</t>
+  </si>
+  <si>
+    <t>ashwinporwal55@gmail.com</t>
+  </si>
+  <si>
+    <t>Ashwin Porwal</t>
+  </si>
+  <si>
+    <t>Anatomy</t>
+  </si>
+  <si>
+    <t>khanakayan039@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayan Khan</t>
+  </si>
+  <si>
+    <t>01kamdar07@gmail.com</t>
+  </si>
+  <si>
+    <t>Yatisha Kamdar</t>
+  </si>
+  <si>
+    <t>reenarathore923@gmail.com</t>
+  </si>
+  <si>
+    <t>Reena Rathore</t>
+  </si>
+  <si>
+    <t>manmohangour638@gmail.com</t>
+  </si>
+  <si>
+    <t>Manmohan Singh Gour</t>
+  </si>
+  <si>
+    <t>1st year</t>
+  </si>
+  <si>
+    <t>abhishekrajpoot68378@gmail.com</t>
+  </si>
+  <si>
+    <t>ABHISHEK DANGI</t>
+  </si>
+  <si>
+    <t>chouhanmayur007@gmail.com</t>
+  </si>
+  <si>
+    <t>Mayur Manoj Chouhan</t>
+  </si>
+  <si>
+    <t>1st year MBBs</t>
+  </si>
+  <si>
+    <t>ramurathor2917@gmail.com</t>
+  </si>
+  <si>
+    <t>Ramprasad Rathor</t>
+  </si>
+  <si>
+    <t>1st year MBBS</t>
+  </si>
+  <si>
+    <t>divyanshi.jindal2@gmail.com</t>
+  </si>
+  <si>
+    <t>Divyanshi Jindal</t>
+  </si>
+  <si>
+    <t>AMALTAS institute of medical sciences</t>
+  </si>
+  <si>
+    <t>nabihahanfi26@gmail.com</t>
+  </si>
+  <si>
+    <t>Nabiha hanfi</t>
+  </si>
+  <si>
+    <t>Forensic medicine</t>
+  </si>
+  <si>
+    <t>sofiashk2509@gmail.com</t>
+  </si>
+  <si>
+    <t>Sofiya shaikh</t>
+  </si>
+  <si>
+    <t>Dr. Geeta vishnariya</t>
+  </si>
+  <si>
+    <t>geetavishnariya@gmail.com</t>
+  </si>
+  <si>
+    <t>Forensic medicine and toxicology</t>
+  </si>
+  <si>
+    <t>dhawaleaman59@gmail.com</t>
+  </si>
+  <si>
+    <t>Aman Dhawale</t>
+  </si>
+  <si>
+    <t>forensicdr0309@gmail.com</t>
+  </si>
+  <si>
+    <t>Radhika Hande</t>
+  </si>
+  <si>
+    <t>AMALTAS INSTITUTE OF MEDICAL SCIENCES</t>
+  </si>
+  <si>
+    <t>Forensic medicine department</t>
+  </si>
+  <si>
+    <t>Dr.Shipra Verma</t>
+  </si>
+  <si>
+    <t>siraverma@gmail.vom</t>
+  </si>
+  <si>
+    <t>Homoeopathic Repertory</t>
+  </si>
+  <si>
+    <t>nanurambhati1213@gmail.com</t>
+  </si>
+  <si>
+    <t>Nanuram Bhatee</t>
+  </si>
+  <si>
+    <t>Staff</t>
+  </si>
+  <si>
+    <t>sagargoel3834@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Sagar Goel</t>
+  </si>
+  <si>
+    <t>Index medical college hospital and research centre</t>
+  </si>
+  <si>
+    <t>General surgery</t>
+  </si>
+  <si>
+    <t>keshavyadav1982@gmail.com</t>
+  </si>
+  <si>
+    <t>keshav yadav</t>
+  </si>
+  <si>
+    <t>Amaltas institute of medical College</t>
+  </si>
+  <si>
+    <t>IT</t>
   </si>
 </sst>
 </file>
@@ -706,7 +1591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -763,6 +1648,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1045,10 +1933,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N241"/>
   <sheetFormatPr defaultColWidth="24" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="68.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="110.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1083,7 +1974,7 @@
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
     </row>
-    <row r="2" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46276.456238425926</v>
       </c>
@@ -1115,7 +2006,7 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
     </row>
-    <row r="3" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>46276.46675925926</v>
       </c>
@@ -1147,7 +2038,7 @@
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
     </row>
-    <row r="4" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46277.462557870371</v>
       </c>
@@ -1179,7 +2070,7 @@
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
     </row>
-    <row r="5" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>46279.406006944446</v>
       </c>
@@ -1211,7 +2102,7 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46279.542395833334</v>
       </c>
@@ -1243,7 +2134,7 @@
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
     </row>
-    <row r="7" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>46279.823298611111</v>
       </c>
@@ -1275,7 +2166,7 @@
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46279.823379629626</v>
       </c>
@@ -1307,7 +2198,7 @@
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>46280.457418981481</v>
       </c>
@@ -1435,7 +2326,7 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>46280.642824074072</v>
       </c>
@@ -1467,7 +2358,7 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>46280.679398148146</v>
       </c>
@@ -1499,7 +2390,7 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>46280.800520833334</v>
       </c>
@@ -1531,7 +2422,7 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>46280.848900462966</v>
       </c>
@@ -1561,7 +2452,7 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>46281.435671296298</v>
       </c>
@@ -1593,7 +2484,7 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>46281.438460648147</v>
       </c>
@@ -1623,7 +2514,7 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>46281.438472222224</v>
       </c>
@@ -1653,7 +2544,7 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>46281.449444444443</v>
       </c>
@@ -1685,7 +2576,7 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>46281.519629629627</v>
       </c>
@@ -1717,7 +2608,7 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>46281.565451388888</v>
       </c>
@@ -1749,7 +2640,7 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>46281.572488425925</v>
       </c>
@@ -1781,7 +2672,7 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>46283.497002314813</v>
       </c>
@@ -1813,7 +2704,7 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>46283.498090277775</v>
       </c>
@@ -1845,7 +2736,7 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>46284.677245370367</v>
       </c>
@@ -1877,7 +2768,7 @@
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>46286.428726851853</v>
       </c>
@@ -1909,7 +2800,7 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>46286.433113425926</v>
       </c>
@@ -1941,7 +2832,7 @@
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>46286.443229166667</v>
       </c>
@@ -1973,7 +2864,7 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>46286.458275462966</v>
       </c>
@@ -2005,7 +2896,7 @@
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
     </row>
-    <row r="31" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>46286.462060185186</v>
       </c>
@@ -2037,7 +2928,7 @@
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>46286.463460648149</v>
       </c>
@@ -2067,7 +2958,7 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
     </row>
-    <row r="33" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>46286.463472222225</v>
       </c>
@@ -2099,7 +2990,7 @@
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
     </row>
-    <row r="34" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>46286.465428240743</v>
       </c>
@@ -2131,7 +3022,7 @@
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>46286.466134259259</v>
       </c>
@@ -2163,7 +3054,7 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>46286.466192129628</v>
       </c>
@@ -2195,29 +3086,29 @@
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
     </row>
-    <row r="37" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="16">
+    <row r="37" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
         <v>46286.467824074076</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="13">
         <v>7049322060</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I37" s="10"/>
@@ -2227,15 +3118,31 @@
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
     </row>
-    <row r="38" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+    <row r="38" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>46286.475659722222</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="8">
+        <v>8827153332</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
@@ -2243,15 +3150,31 @@
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
     </row>
-    <row r="39" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+    <row r="39" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11">
+        <v>46286.479803240742</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="13">
+        <v>9770721526</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
@@ -2259,15 +3182,31 @@
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
     </row>
-    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+    <row r="40" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
+        <v>46286.483159722222</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="8">
+        <v>9340491330</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
@@ -2275,15 +3214,31 @@
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
     </row>
-    <row r="41" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
+    <row r="41" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11">
+        <v>46286.483599537038</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="13">
+        <v>8103887628</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
@@ -2291,15 +3246,31 @@
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
     </row>
-    <row r="42" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+    <row r="42" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
+        <v>46286.494652777779</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="8">
+        <v>7974275417</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
@@ -2307,15 +3278,31 @@
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+    <row r="43" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
+        <v>46286.505624999998</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="13">
+        <v>7389707692</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
@@ -2323,15 +3310,31 @@
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
     </row>
-    <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+    <row r="44" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
+        <v>46286.516851851855</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="8">
+        <v>9827447484</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
@@ -2339,15 +3342,31 @@
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
     </row>
-    <row r="45" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+    <row r="45" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11">
+        <v>46286.528969907406</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="13">
+        <v>9826823825</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
@@ -2355,15 +3374,31 @@
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
     </row>
-    <row r="46" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+    <row r="46" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
+        <v>46286.529710648145</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="8">
+        <v>9098660715</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
@@ -2371,15 +3406,31 @@
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
     </row>
-    <row r="47" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+    <row r="47" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11">
+        <v>46286.538368055553</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" s="13">
+        <v>8319505243</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
@@ -2387,15 +3438,31 @@
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
     </row>
-    <row r="48" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+    <row r="48" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
+        <v>46286.538414351853</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="8">
+        <v>8085952768</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
@@ -2403,15 +3470,31 @@
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
     </row>
-    <row r="49" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+    <row r="49" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11">
+        <v>46286.549930555557</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" s="13">
+        <v>6265282876</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
@@ -2419,15 +3502,31 @@
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
     </row>
-    <row r="50" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+    <row r="50" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
+        <v>46286.557534722226</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D50" s="8">
+        <v>8600506762</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
@@ -2435,15 +3534,31 @@
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
     </row>
-    <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+    <row r="51" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
+        <v>46286.570185185185</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="13">
+        <v>9893950423</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
@@ -2451,15 +3566,31 @@
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
     </row>
-    <row r="52" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+    <row r="52" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
+        <v>46286.572002314817</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" s="8">
+        <v>9074207267</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
@@ -2467,15 +3598,31 @@
       <c r="M52" s="10"/>
       <c r="N52" s="10"/>
     </row>
-    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
+    <row r="53" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11">
+        <v>46286.597708333335</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D53" s="13">
+        <v>9403723176</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
@@ -2483,15 +3630,31 @@
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
     </row>
-    <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
+    <row r="54" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
+        <v>46286.607245370367</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D54" s="8">
+        <v>6261683816</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
@@ -2499,15 +3662,31 @@
       <c r="M54" s="10"/>
       <c r="N54" s="10"/>
     </row>
-    <row r="55" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+    <row r="55" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11">
+        <v>46286.610462962963</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55" s="13">
+        <v>6264588710</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
@@ -2515,15 +3694,31 @@
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
     </row>
-    <row r="56" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+    <row r="56" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
+        <v>46286.643148148149</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" s="8">
+        <v>9755636785</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
@@ -2531,15 +3726,31 @@
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
     </row>
-    <row r="57" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+    <row r="57" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11">
+        <v>46286.662708333337</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D57" s="13">
+        <v>9399214429</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
@@ -2547,15 +3758,31 @@
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="10"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
+    <row r="58" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
+        <v>46286.671041666668</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="8">
+        <v>9650956946</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
@@ -2563,15 +3790,31 @@
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
     </row>
-    <row r="59" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+    <row r="59" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
+        <v>46286.672106481485</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D59" s="13">
+        <v>7879388387</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
@@ -2579,15 +3822,31 @@
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
     </row>
-    <row r="60" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+    <row r="60" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
+        <v>46286.673877314817</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="8">
+        <v>9399876670</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
@@ -2595,15 +3854,31 @@
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
     </row>
-    <row r="61" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
+    <row r="61" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11">
+        <v>46286.677847222221</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" s="13">
+        <v>7771944147</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
@@ -2611,15 +3886,29 @@
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
     </row>
-    <row r="62" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+    <row r="62" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
+        <v>46286.681018518517</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D62" s="8">
+        <v>7389091275</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
@@ -2627,15 +3916,31 @@
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
     </row>
-    <row r="63" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+    <row r="63" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
+        <v>46286.6874537037</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D63" s="13">
+        <v>9669255995</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
@@ -2643,15 +3948,31 @@
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+    <row r="64" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
+        <v>46286.688344907408</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D64" s="8">
+        <v>8769312252</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
@@ -2659,15 +3980,31 @@
       <c r="M64" s="10"/>
       <c r="N64" s="10"/>
     </row>
-    <row r="65" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+    <row r="65" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
+        <v>46286.718842592592</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D65" s="13">
+        <v>9755385125</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
@@ -2675,15 +4012,31 @@
       <c r="M65" s="10"/>
       <c r="N65" s="10"/>
     </row>
-    <row r="66" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
+    <row r="66" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="5">
+        <v>46286.726863425924</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D66" s="8">
+        <v>9589467628</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
@@ -2691,15 +4044,31 @@
       <c r="M66" s="10"/>
       <c r="N66" s="10"/>
     </row>
-    <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
+    <row r="67" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11">
+        <v>46286.736041666663</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D67" s="13">
+        <v>7879068805</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
@@ -2707,15 +4076,31 @@
       <c r="M67" s="10"/>
       <c r="N67" s="10"/>
     </row>
-    <row r="68" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="10"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
+    <row r="68" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="5">
+        <v>46286.738865740743</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D68" s="8">
+        <v>8770439781</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
@@ -2723,15 +4108,31 @@
       <c r="M68" s="10"/>
       <c r="N68" s="10"/>
     </row>
-    <row r="69" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="10"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
+    <row r="69" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="11">
+        <v>46286.762175925927</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D69" s="13">
+        <v>9421972027</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
@@ -2739,15 +4140,29 @@
       <c r="M69" s="10"/>
       <c r="N69" s="10"/>
     </row>
-    <row r="70" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="10"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
+    <row r="70" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="5">
+        <v>46286.769560185188</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D70" s="8">
+        <v>8602285582</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="G70" s="6"/>
+      <c r="H70" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
@@ -2755,15 +4170,31 @@
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
     </row>
-    <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="10"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
+    <row r="71" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11">
+        <v>46286.802800925929</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D71" s="13">
+        <v>8604994851</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
@@ -2771,15 +4202,31 @@
       <c r="M71" s="10"/>
       <c r="N71" s="10"/>
     </row>
-    <row r="72" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="10"/>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
+    <row r="72" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
+        <v>46286.810185185182</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D72" s="8">
+        <v>7507594401</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
@@ -2787,15 +4234,31 @@
       <c r="M72" s="10"/>
       <c r="N72" s="10"/>
     </row>
-    <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
+    <row r="73" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
+        <v>46286.811238425929</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D73" s="13">
+        <v>9669647299</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
@@ -2803,15 +4266,31 @@
       <c r="M73" s="10"/>
       <c r="N73" s="10"/>
     </row>
-    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="10"/>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
+    <row r="74" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="5">
+        <v>46286.812847222223</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D74" s="8">
+        <v>9826485575</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
@@ -2819,15 +4298,31 @@
       <c r="M74" s="10"/>
       <c r="N74" s="10"/>
     </row>
-    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="10"/>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
+    <row r="75" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11">
+        <v>46286.830914351849</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D75" s="13">
+        <v>8108093689</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
@@ -2835,15 +4330,31 @@
       <c r="M75" s="10"/>
       <c r="N75" s="10"/>
     </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
+    <row r="76" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="5">
+        <v>46286.907835648148</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D76" s="8">
+        <v>9907301233</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
@@ -2851,15 +4362,31 @@
       <c r="M76" s="10"/>
       <c r="N76" s="10"/>
     </row>
-    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="10"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
+    <row r="77" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="11">
+        <v>46286.913773148146</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D77" s="13">
+        <v>9644472700</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
@@ -2867,15 +4394,31 @@
       <c r="M77" s="10"/>
       <c r="N77" s="10"/>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
+    <row r="78" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="5">
+        <v>46286.919895833336</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D78" s="8">
+        <v>9826098266</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
@@ -2883,15 +4426,31 @@
       <c r="M78" s="10"/>
       <c r="N78" s="10"/>
     </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
+    <row r="79" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11">
+        <v>46286.952638888892</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" s="12">
+        <v>9039845158</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
@@ -2899,15 +4458,31 @@
       <c r="M79" s="10"/>
       <c r="N79" s="10"/>
     </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
+    <row r="80" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="5">
+        <v>46287.011550925927</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D80" s="8">
+        <v>9009124535</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
@@ -2915,15 +4490,31 @@
       <c r="M80" s="10"/>
       <c r="N80" s="10"/>
     </row>
-    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
+    <row r="81" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11">
+        <v>46287.309062499997</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D81" s="13">
+        <v>9893537533</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
@@ -2931,15 +4522,31 @@
       <c r="M81" s="10"/>
       <c r="N81" s="10"/>
     </row>
-    <row r="82" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
+    <row r="82" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="5">
+        <v>46287.341782407406</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D82" s="8">
+        <v>8085616332</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
@@ -2947,15 +4554,31 @@
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
     </row>
-    <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
+    <row r="83" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11">
+        <v>46287.347037037034</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D83" s="13">
+        <v>8085838584</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
@@ -2963,15 +4586,29 @@
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
     </row>
-    <row r="84" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
+    <row r="84" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="5">
+        <v>46287.354548611111</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D84" s="8">
+        <v>8982293900</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G84" s="6"/>
+      <c r="H84" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
@@ -2979,15 +4616,31 @@
       <c r="M84" s="10"/>
       <c r="N84" s="10"/>
     </row>
-    <row r="85" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
+    <row r="85" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="11">
+        <v>46287.379583333335</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D85" s="13">
+        <v>942548277</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
@@ -2995,15 +4648,31 @@
       <c r="M85" s="10"/>
       <c r="N85" s="10"/>
     </row>
-    <row r="86" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
+    <row r="86" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
+        <v>46287.383101851854</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D86" s="8">
+        <v>8085296585</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
@@ -3011,15 +4680,31 @@
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
     </row>
-    <row r="87" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
+    <row r="87" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
+        <v>46287.39130787037</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D87" s="13">
+        <v>9926841097</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
       <c r="K87" s="10"/>
@@ -3027,15 +4712,31 @@
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
     </row>
-    <row r="88" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
+    <row r="88" spans="1:14" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="5">
+        <v>46287.392696759256</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D88" s="8">
+        <v>7987617445</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10"/>
@@ -3043,15 +4744,31 @@
       <c r="M88" s="10"/>
       <c r="N88" s="10"/>
     </row>
-    <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
+    <row r="89" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11">
+        <v>46287.410173611112</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="D89" s="13">
+        <v>6265478701</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
@@ -3059,15 +4776,31 @@
       <c r="M89" s="10"/>
       <c r="N89" s="10"/>
     </row>
-    <row r="90" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
+    <row r="90" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5">
+        <v>46287.424872685187</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D90" s="8">
+        <v>9818783535</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10"/>
@@ -3075,15 +4808,31 @@
       <c r="M90" s="10"/>
       <c r="N90" s="10"/>
     </row>
-    <row r="91" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
+    <row r="91" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11">
+        <v>46287.432881944442</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D91" s="13">
+        <v>7999951869</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10"/>
@@ -3091,15 +4840,31 @@
       <c r="M91" s="10"/>
       <c r="N91" s="10"/>
     </row>
-    <row r="92" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
+    <row r="92" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="5">
+        <v>46287.437962962962</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D92" s="8">
+        <v>9011196096</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
       <c r="K92" s="10"/>
@@ -3107,15 +4872,31 @@
       <c r="M92" s="10"/>
       <c r="N92" s="10"/>
     </row>
-    <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
+    <row r="93" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11">
+        <v>46287.442233796297</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D93" s="13">
+        <v>9584826515</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
@@ -3123,15 +4904,31 @@
       <c r="M93" s="10"/>
       <c r="N93" s="10"/>
     </row>
-    <row r="94" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
+    <row r="94" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="5">
+        <v>46287.449861111112</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D94" s="8">
+        <v>9109620468</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I94" s="10"/>
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
@@ -3139,15 +4936,31 @@
       <c r="M94" s="10"/>
       <c r="N94" s="10"/>
     </row>
-    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
+    <row r="95" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11">
+        <v>46287.461458333331</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D95" s="12">
+        <v>7869641536</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
@@ -3155,15 +4968,31 @@
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
     </row>
-    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
+    <row r="96" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="5">
+        <v>46287.483541666668</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D96" s="8">
+        <v>9826247595</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
       <c r="K96" s="10"/>
@@ -3171,15 +5000,29 @@
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
     </row>
-    <row r="97" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10"/>
+    <row r="97" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11">
+        <v>46287.496481481481</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="D97" s="13">
+        <v>8718071971</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G97" s="15"/>
+      <c r="H97" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
@@ -3187,15 +5030,31 @@
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
     </row>
-    <row r="98" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="10"/>
-      <c r="H98" s="10"/>
+    <row r="98" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5">
+        <v>46287.498055555552</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D98" s="8">
+        <v>6264562405</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I98" s="10"/>
       <c r="J98" s="10"/>
       <c r="K98" s="10"/>
@@ -3203,15 +5062,31 @@
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
     </row>
-    <row r="99" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
+    <row r="99" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="11">
+        <v>46287.498611111114</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="D99" s="13">
+        <v>9303124916</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10"/>
@@ -3219,15 +5094,29 @@
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
     </row>
-    <row r="100" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
+    <row r="100" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5">
+        <v>46287.498807870368</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D100" s="8">
+        <v>9343559211</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="G100" s="6"/>
+      <c r="H100" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
       <c r="K100" s="10"/>
@@ -3235,15 +5124,31 @@
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
     </row>
-    <row r="101" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
+    <row r="101" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="11">
+        <v>46287.498819444445</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="D101" s="13">
+        <v>9424311816</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I101" s="10"/>
       <c r="J101" s="10"/>
       <c r="K101" s="10"/>
@@ -3251,15 +5156,29 @@
       <c r="M101" s="10"/>
       <c r="N101" s="10"/>
     </row>
-    <row r="102" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="10"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="10"/>
-      <c r="H102" s="10"/>
+    <row r="102" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="5">
+        <v>46287.498819444445</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D102" s="8">
+        <v>6265345452</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G102" s="6"/>
+      <c r="H102" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
@@ -3267,15 +5186,31 @@
       <c r="M102" s="10"/>
       <c r="N102" s="10"/>
     </row>
-    <row r="103" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-      <c r="E103" s="10"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="10"/>
+    <row r="103" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="11">
+        <v>46287.498981481483</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D103" s="13">
+        <v>8871522540</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I103" s="10"/>
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
@@ -3283,15 +5218,31 @@
       <c r="M103" s="10"/>
       <c r="N103" s="10"/>
     </row>
-    <row r="104" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
+    <row r="104" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="5">
+        <v>46287.498981481483</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D104" s="8">
+        <v>9302626787</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
@@ -3299,15 +5250,31 @@
       <c r="M104" s="10"/>
       <c r="N104" s="10"/>
     </row>
-    <row r="105" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="10"/>
-      <c r="H105" s="10"/>
+    <row r="105" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11">
+        <v>46287.49900462963</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D105" s="13">
+        <v>7440499373</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
@@ -3315,15 +5282,31 @@
       <c r="M105" s="10"/>
       <c r="N105" s="10"/>
     </row>
-    <row r="106" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="10"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="10"/>
-      <c r="H106" s="10"/>
+    <row r="106" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="5">
+        <v>46287.499120370368</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D106" s="8">
+        <v>8823045577</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10"/>
@@ -3331,15 +5314,31 @@
       <c r="M106" s="10"/>
       <c r="N106" s="10"/>
     </row>
-    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
+    <row r="107" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11">
+        <v>46287.499166666668</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D107" s="12">
+        <v>6261476209</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
@@ -3347,15 +5346,31 @@
       <c r="M107" s="10"/>
       <c r="N107" s="10"/>
     </row>
-    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
+    <row r="108" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5">
+        <v>46287.499201388891</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D108" s="8">
+        <v>8962084676</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10"/>
@@ -3363,15 +5378,31 @@
       <c r="M108" s="10"/>
       <c r="N108" s="10"/>
     </row>
-    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
+    <row r="109" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="11">
+        <v>46287.499247685184</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="D109" s="13">
+        <v>9826454975</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G109" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H109" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
@@ -3379,15 +5410,31 @@
       <c r="M109" s="10"/>
       <c r="N109" s="10"/>
     </row>
-    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10"/>
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
+    <row r="110" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="5">
+        <v>46287.49931712963</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D110" s="8">
+        <v>9755166294</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I110" s="10"/>
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
@@ -3395,15 +5442,31 @@
       <c r="M110" s="10"/>
       <c r="N110" s="10"/>
     </row>
-    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="10"/>
-      <c r="B111" s="10"/>
-      <c r="C111" s="10"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
+    <row r="111" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="11">
+        <v>46287.499444444446</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D111" s="13">
+        <v>8827263117</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="H111" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
@@ -3411,15 +5474,31 @@
       <c r="M111" s="10"/>
       <c r="N111" s="10"/>
     </row>
-    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
+    <row r="112" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="5">
+        <v>46287.499456018515</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D112" s="8">
+        <v>9826048340</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I112" s="10"/>
       <c r="J112" s="10"/>
       <c r="K112" s="10"/>
@@ -3427,15 +5506,31 @@
       <c r="M112" s="10"/>
       <c r="N112" s="10"/>
     </row>
-    <row r="113" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="10"/>
-      <c r="B113" s="10"/>
-      <c r="C113" s="10"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
+    <row r="113" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="11">
+        <v>46287.499467592592</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D113" s="13">
+        <v>9575291197</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H113" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I113" s="10"/>
       <c r="J113" s="10"/>
       <c r="K113" s="10"/>
@@ -3443,15 +5538,31 @@
       <c r="M113" s="10"/>
       <c r="N113" s="10"/>
     </row>
-    <row r="114" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="10"/>
-      <c r="B114" s="10"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10"/>
+    <row r="114" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="5">
+        <v>46287.499479166669</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D114" s="8">
+        <v>9238990644</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="I114" s="10"/>
       <c r="J114" s="10"/>
       <c r="K114" s="10"/>
@@ -3459,15 +5570,31 @@
       <c r="M114" s="10"/>
       <c r="N114" s="10"/>
     </row>
-    <row r="115" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="10"/>
-      <c r="G115" s="10"/>
-      <c r="H115" s="10"/>
+    <row r="115" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="11">
+        <v>46287.499502314815</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D115" s="13">
+        <v>9685602221</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H115" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I115" s="10"/>
       <c r="J115" s="10"/>
       <c r="K115" s="10"/>
@@ -3475,15 +5602,31 @@
       <c r="M115" s="10"/>
       <c r="N115" s="10"/>
     </row>
-    <row r="116" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="10"/>
-      <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="10"/>
-      <c r="G116" s="10"/>
-      <c r="H116" s="10"/>
+    <row r="116" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="5">
+        <v>46287.499826388892</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="D116" s="8">
+        <v>7000855737</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I116" s="10"/>
       <c r="J116" s="10"/>
       <c r="K116" s="10"/>
@@ -3491,15 +5634,31 @@
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
     </row>
-    <row r="117" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="10"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="10"/>
-      <c r="G117" s="10"/>
-      <c r="H117" s="10"/>
+    <row r="117" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="11">
+        <v>46287.4999537037</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D117" s="13">
+        <v>9109140397</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="H117" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="I117" s="10"/>
       <c r="J117" s="10"/>
       <c r="K117" s="10"/>
@@ -3507,15 +5666,31 @@
       <c r="M117" s="10"/>
       <c r="N117" s="10"/>
     </row>
-    <row r="118" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="10"/>
-      <c r="E118" s="10"/>
-      <c r="F118" s="10"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="10"/>
+    <row r="118" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="5">
+        <v>46287.500243055554</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D118" s="8">
+        <v>8358947234</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I118" s="10"/>
       <c r="J118" s="10"/>
       <c r="K118" s="10"/>
@@ -3523,15 +5698,31 @@
       <c r="M118" s="10"/>
       <c r="N118" s="10"/>
     </row>
-    <row r="119" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="10"/>
-      <c r="E119" s="10"/>
-      <c r="F119" s="10"/>
-      <c r="G119" s="10"/>
-      <c r="H119" s="10"/>
+    <row r="119" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="11">
+        <v>46287.500358796293</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D119" s="13">
+        <v>7869277105</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H119" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I119" s="10"/>
       <c r="J119" s="10"/>
       <c r="K119" s="10"/>
@@ -3539,15 +5730,31 @@
       <c r="M119" s="10"/>
       <c r="N119" s="10"/>
     </row>
-    <row r="120" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="10"/>
-      <c r="B120" s="10"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="10"/>
-      <c r="E120" s="10"/>
-      <c r="F120" s="10"/>
-      <c r="G120" s="10"/>
-      <c r="H120" s="10"/>
+    <row r="120" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="5">
+        <v>46287.500405092593</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="D120" s="8">
+        <v>8435099368</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I120" s="10"/>
       <c r="J120" s="10"/>
       <c r="K120" s="10"/>
@@ -3555,15 +5762,31 @@
       <c r="M120" s="10"/>
       <c r="N120" s="10"/>
     </row>
-    <row r="121" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="10"/>
-      <c r="B121" s="10"/>
-      <c r="C121" s="10"/>
-      <c r="D121" s="10"/>
-      <c r="E121" s="10"/>
-      <c r="F121" s="10"/>
-      <c r="G121" s="10"/>
-      <c r="H121" s="10"/>
+    <row r="121" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="11">
+        <v>46287.501099537039</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D121" s="13">
+        <v>9329489766</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I121" s="10"/>
       <c r="J121" s="10"/>
       <c r="K121" s="10"/>
@@ -3571,15 +5794,29 @@
       <c r="M121" s="10"/>
       <c r="N121" s="10"/>
     </row>
-    <row r="122" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="10"/>
-      <c r="E122" s="10"/>
-      <c r="F122" s="10"/>
-      <c r="G122" s="10"/>
-      <c r="H122" s="10"/>
+    <row r="122" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="5">
+        <v>46287.501504629632</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D122" s="8">
+        <v>9039980987</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G122" s="6"/>
+      <c r="H122" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I122" s="10"/>
       <c r="J122" s="10"/>
       <c r="K122" s="10"/>
@@ -3587,15 +5824,31 @@
       <c r="M122" s="10"/>
       <c r="N122" s="10"/>
     </row>
-    <row r="123" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="10"/>
-      <c r="B123" s="10"/>
-      <c r="C123" s="10"/>
-      <c r="D123" s="10"/>
-      <c r="E123" s="10"/>
-      <c r="F123" s="10"/>
-      <c r="G123" s="10"/>
-      <c r="H123" s="10"/>
+    <row r="123" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="11">
+        <v>46287.504212962966</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="D123" s="13">
+        <v>9201055469</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H123" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I123" s="10"/>
       <c r="J123" s="10"/>
       <c r="K123" s="10"/>
@@ -3603,15 +5856,31 @@
       <c r="M123" s="10"/>
       <c r="N123" s="10"/>
     </row>
-    <row r="124" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="10"/>
-      <c r="G124" s="10"/>
-      <c r="H124" s="10"/>
+    <row r="124" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="5">
+        <v>46287.507303240738</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D124" s="8">
+        <v>8225051059</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I124" s="10"/>
       <c r="J124" s="10"/>
       <c r="K124" s="10"/>
@@ -3619,15 +5888,29 @@
       <c r="M124" s="10"/>
       <c r="N124" s="10"/>
     </row>
-    <row r="125" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="10"/>
-      <c r="B125" s="10"/>
-      <c r="C125" s="10"/>
-      <c r="D125" s="10"/>
-      <c r="E125" s="10"/>
-      <c r="F125" s="10"/>
-      <c r="G125" s="10"/>
-      <c r="H125" s="10"/>
+    <row r="125" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="11">
+        <v>46287.529606481483</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D125" s="13">
+        <v>7828267992</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="G125" s="15"/>
+      <c r="H125" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I125" s="10"/>
       <c r="J125" s="10"/>
       <c r="K125" s="10"/>
@@ -3635,15 +5918,29 @@
       <c r="M125" s="10"/>
       <c r="N125" s="10"/>
     </row>
-    <row r="126" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="10"/>
-      <c r="B126" s="10"/>
-      <c r="C126" s="10"/>
-      <c r="D126" s="10"/>
-      <c r="E126" s="10"/>
-      <c r="F126" s="10"/>
-      <c r="G126" s="10"/>
-      <c r="H126" s="10"/>
+    <row r="126" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="5">
+        <v>46287.530057870368</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D126" s="8">
+        <v>9340401498</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="G126" s="6"/>
+      <c r="H126" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I126" s="10"/>
       <c r="J126" s="10"/>
       <c r="K126" s="10"/>
@@ -3651,15 +5948,31 @@
       <c r="M126" s="10"/>
       <c r="N126" s="10"/>
     </row>
-    <row r="127" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="10"/>
-      <c r="B127" s="10"/>
-      <c r="C127" s="10"/>
-      <c r="D127" s="10"/>
-      <c r="E127" s="10"/>
-      <c r="F127" s="10"/>
-      <c r="G127" s="10"/>
-      <c r="H127" s="10"/>
+    <row r="127" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="11">
+        <v>46287.533796296295</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D127" s="13">
+        <v>8959350311</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G127" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H127" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="10"/>
@@ -3667,15 +5980,31 @@
       <c r="M127" s="10"/>
       <c r="N127" s="10"/>
     </row>
-    <row r="128" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10"/>
-      <c r="C128" s="10"/>
-      <c r="D128" s="10"/>
-      <c r="E128" s="10"/>
-      <c r="F128" s="10"/>
-      <c r="G128" s="10"/>
-      <c r="H128" s="10"/>
+    <row r="128" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="5">
+        <v>46287.546041666668</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D128" s="8">
+        <v>9630469660</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I128" s="10"/>
       <c r="J128" s="10"/>
       <c r="K128" s="10"/>
@@ -3683,15 +6012,29 @@
       <c r="M128" s="10"/>
       <c r="N128" s="10"/>
     </row>
-    <row r="129" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="10"/>
-      <c r="B129" s="10"/>
-      <c r="C129" s="10"/>
-      <c r="D129" s="10"/>
-      <c r="E129" s="10"/>
-      <c r="F129" s="10"/>
-      <c r="G129" s="10"/>
-      <c r="H129" s="10"/>
+    <row r="129" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="11">
+        <v>46287.546655092592</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D129" s="13">
+        <v>7879894457</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="G129" s="15"/>
+      <c r="H129" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I129" s="10"/>
       <c r="J129" s="10"/>
       <c r="K129" s="10"/>
@@ -3699,15 +6042,31 @@
       <c r="M129" s="10"/>
       <c r="N129" s="10"/>
     </row>
-    <row r="130" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="10"/>
-      <c r="B130" s="10"/>
-      <c r="C130" s="10"/>
-      <c r="D130" s="10"/>
-      <c r="E130" s="10"/>
-      <c r="F130" s="10"/>
-      <c r="G130" s="10"/>
-      <c r="H130" s="10"/>
+    <row r="130" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="5">
+        <v>46287.549189814818</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="D130" s="8">
+        <v>8305053515</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I130" s="10"/>
       <c r="J130" s="10"/>
       <c r="K130" s="10"/>
@@ -3715,15 +6074,31 @@
       <c r="M130" s="10"/>
       <c r="N130" s="10"/>
     </row>
-    <row r="131" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="10"/>
-      <c r="B131" s="10"/>
-      <c r="C131" s="10"/>
-      <c r="D131" s="10"/>
-      <c r="E131" s="10"/>
-      <c r="F131" s="10"/>
-      <c r="G131" s="10"/>
-      <c r="H131" s="10"/>
+    <row r="131" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="11">
+        <v>46287.551087962966</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="D131" s="13">
+        <v>6265988946</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G131" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="H131" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I131" s="10"/>
       <c r="J131" s="10"/>
       <c r="K131" s="10"/>
@@ -3731,15 +6106,31 @@
       <c r="M131" s="10"/>
       <c r="N131" s="10"/>
     </row>
-    <row r="132" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="10"/>
-      <c r="B132" s="10"/>
-      <c r="C132" s="10"/>
-      <c r="D132" s="10"/>
-      <c r="E132" s="10"/>
-      <c r="F132" s="10"/>
-      <c r="G132" s="10"/>
-      <c r="H132" s="10"/>
+    <row r="132" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="5">
+        <v>46287.555775462963</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D132" s="8">
+        <v>8209218887</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I132" s="10"/>
       <c r="J132" s="10"/>
       <c r="K132" s="10"/>
@@ -3747,15 +6138,31 @@
       <c r="M132" s="10"/>
       <c r="N132" s="10"/>
     </row>
-    <row r="133" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
-      <c r="C133" s="10"/>
-      <c r="D133" s="10"/>
-      <c r="E133" s="10"/>
-      <c r="F133" s="10"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10"/>
+    <row r="133" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="11">
+        <v>46287.557141203702</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D133" s="13">
+        <v>7024922374</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="G133" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H133" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I133" s="10"/>
       <c r="J133" s="10"/>
       <c r="K133" s="10"/>
@@ -3763,15 +6170,31 @@
       <c r="M133" s="10"/>
       <c r="N133" s="10"/>
     </row>
-    <row r="134" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="10"/>
-      <c r="B134" s="10"/>
-      <c r="C134" s="10"/>
-      <c r="D134" s="10"/>
-      <c r="E134" s="10"/>
-      <c r="F134" s="10"/>
-      <c r="G134" s="10"/>
-      <c r="H134" s="10"/>
+    <row r="134" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="5">
+        <v>46287.557962962965</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="D134" s="8">
+        <v>7828720107</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I134" s="10"/>
       <c r="J134" s="10"/>
       <c r="K134" s="10"/>
@@ -3779,15 +6202,31 @@
       <c r="M134" s="10"/>
       <c r="N134" s="10"/>
     </row>
-    <row r="135" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="10"/>
-      <c r="B135" s="10"/>
-      <c r="C135" s="10"/>
-      <c r="D135" s="10"/>
-      <c r="E135" s="10"/>
-      <c r="F135" s="10"/>
-      <c r="G135" s="10"/>
-      <c r="H135" s="10"/>
+    <row r="135" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="11">
+        <v>46287.558032407411</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="D135" s="13">
+        <v>9826244142</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H135" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I135" s="10"/>
       <c r="J135" s="10"/>
       <c r="K135" s="10"/>
@@ -3795,15 +6234,31 @@
       <c r="M135" s="10"/>
       <c r="N135" s="10"/>
     </row>
-    <row r="136" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="10"/>
-      <c r="B136" s="10"/>
-      <c r="C136" s="10"/>
-      <c r="D136" s="10"/>
-      <c r="E136" s="10"/>
-      <c r="F136" s="10"/>
-      <c r="G136" s="10"/>
-      <c r="H136" s="10"/>
+    <row r="136" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="5">
+        <v>46287.565937500003</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D136" s="8">
+        <v>9146367672</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I136" s="10"/>
       <c r="J136" s="10"/>
       <c r="K136" s="10"/>
@@ -3811,15 +6266,31 @@
       <c r="M136" s="10"/>
       <c r="N136" s="10"/>
     </row>
-    <row r="137" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="10"/>
-      <c r="B137" s="10"/>
-      <c r="C137" s="10"/>
-      <c r="D137" s="10"/>
-      <c r="E137" s="10"/>
-      <c r="F137" s="10"/>
-      <c r="G137" s="10"/>
-      <c r="H137" s="10"/>
+    <row r="137" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="11">
+        <v>46287.566076388888</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="D137" s="13">
+        <v>8779057521</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="G137" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H137" s="14" t="s">
+        <v>13</v>
+      </c>
       <c r="I137" s="10"/>
       <c r="J137" s="10"/>
       <c r="K137" s="10"/>
@@ -3827,6 +6298,1732 @@
       <c r="M137" s="10"/>
       <c r="N137" s="10"/>
     </row>
+    <row r="138" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="5">
+        <v>46287.566655092596</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D138" s="8">
+        <v>8318055816</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138" s="10"/>
+      <c r="J138" s="10"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="10"/>
+      <c r="M138" s="10"/>
+      <c r="N138" s="10"/>
+    </row>
+    <row r="139" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="11">
+        <v>46287.571446759262</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="D139" s="13">
+        <v>8462998828</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G139" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="H139" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="10"/>
+      <c r="J139" s="10"/>
+      <c r="K139" s="10"/>
+      <c r="L139" s="10"/>
+      <c r="M139" s="10"/>
+      <c r="N139" s="10"/>
+    </row>
+    <row r="140" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="5">
+        <v>46287.575590277775</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D140" s="8">
+        <v>9350207061</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I140" s="10"/>
+      <c r="J140" s="10"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="10"/>
+      <c r="M140" s="10"/>
+      <c r="N140" s="10"/>
+    </row>
+    <row r="141" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="16">
+        <v>46287.599768518521</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="D141" s="18">
+        <v>7566025599</v>
+      </c>
+      <c r="E141" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="F141" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="G141" s="20"/>
+      <c r="H141" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141" s="10"/>
+      <c r="J141" s="10"/>
+      <c r="K141" s="10"/>
+      <c r="L141" s="10"/>
+      <c r="M141" s="10"/>
+      <c r="N141" s="10"/>
+    </row>
+    <row r="142" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="10"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10"/>
+      <c r="H142" s="10"/>
+      <c r="I142" s="10"/>
+      <c r="J142" s="10"/>
+      <c r="K142" s="10"/>
+      <c r="L142" s="10"/>
+      <c r="M142" s="10"/>
+      <c r="N142" s="10"/>
+    </row>
+    <row r="143" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="10"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+      <c r="G143" s="10"/>
+      <c r="H143" s="10"/>
+      <c r="I143" s="10"/>
+      <c r="J143" s="10"/>
+      <c r="K143" s="10"/>
+      <c r="L143" s="10"/>
+      <c r="M143" s="10"/>
+      <c r="N143" s="10"/>
+    </row>
+    <row r="144" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="10"/>
+      <c r="B144" s="10"/>
+      <c r="C144" s="10"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
+      <c r="G144" s="10"/>
+      <c r="H144" s="10"/>
+      <c r="I144" s="10"/>
+      <c r="J144" s="10"/>
+      <c r="K144" s="10"/>
+      <c r="L144" s="10"/>
+      <c r="M144" s="10"/>
+      <c r="N144" s="10"/>
+    </row>
+    <row r="145" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="10"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10"/>
+      <c r="H145" s="10"/>
+      <c r="I145" s="10"/>
+      <c r="J145" s="10"/>
+      <c r="K145" s="10"/>
+      <c r="L145" s="10"/>
+      <c r="M145" s="10"/>
+      <c r="N145" s="10"/>
+    </row>
+    <row r="146" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="10"/>
+      <c r="B146" s="10"/>
+      <c r="C146" s="10"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
+      <c r="G146" s="10"/>
+      <c r="H146" s="10"/>
+      <c r="I146" s="10"/>
+      <c r="J146" s="10"/>
+      <c r="K146" s="10"/>
+      <c r="L146" s="10"/>
+      <c r="M146" s="10"/>
+      <c r="N146" s="10"/>
+    </row>
+    <row r="147" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="10"/>
+      <c r="B147" s="10"/>
+      <c r="C147" s="10"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
+      <c r="G147" s="10"/>
+      <c r="H147" s="10"/>
+      <c r="I147" s="10"/>
+      <c r="J147" s="10"/>
+      <c r="K147" s="10"/>
+      <c r="L147" s="10"/>
+      <c r="M147" s="10"/>
+      <c r="N147" s="10"/>
+    </row>
+    <row r="148" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="10"/>
+      <c r="B148" s="10"/>
+      <c r="C148" s="10"/>
+      <c r="D148" s="10"/>
+      <c r="E148" s="10"/>
+      <c r="F148" s="10"/>
+      <c r="G148" s="10"/>
+      <c r="H148" s="10"/>
+      <c r="I148" s="10"/>
+      <c r="J148" s="10"/>
+      <c r="K148" s="10"/>
+      <c r="L148" s="10"/>
+      <c r="M148" s="10"/>
+      <c r="N148" s="10"/>
+    </row>
+    <row r="149" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="10"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
+      <c r="G149" s="10"/>
+      <c r="H149" s="10"/>
+      <c r="I149" s="10"/>
+      <c r="J149" s="10"/>
+      <c r="K149" s="10"/>
+      <c r="L149" s="10"/>
+      <c r="M149" s="10"/>
+      <c r="N149" s="10"/>
+    </row>
+    <row r="150" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="10"/>
+      <c r="H150" s="10"/>
+      <c r="I150" s="10"/>
+      <c r="J150" s="10"/>
+      <c r="K150" s="10"/>
+      <c r="L150" s="10"/>
+      <c r="M150" s="10"/>
+      <c r="N150" s="10"/>
+    </row>
+    <row r="151" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="10"/>
+      <c r="B151" s="10"/>
+      <c r="C151" s="10"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="10"/>
+      <c r="F151" s="10"/>
+      <c r="G151" s="10"/>
+      <c r="H151" s="10"/>
+      <c r="I151" s="10"/>
+      <c r="J151" s="10"/>
+      <c r="K151" s="10"/>
+      <c r="L151" s="10"/>
+      <c r="M151" s="10"/>
+      <c r="N151" s="10"/>
+    </row>
+    <row r="152" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="10"/>
+      <c r="B152" s="10"/>
+      <c r="C152" s="10"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
+      <c r="G152" s="10"/>
+      <c r="H152" s="10"/>
+      <c r="I152" s="10"/>
+      <c r="J152" s="10"/>
+      <c r="K152" s="10"/>
+      <c r="L152" s="10"/>
+      <c r="M152" s="10"/>
+      <c r="N152" s="10"/>
+    </row>
+    <row r="153" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="10"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="10"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="10"/>
+      <c r="F153" s="10"/>
+      <c r="G153" s="10"/>
+      <c r="H153" s="10"/>
+      <c r="I153" s="10"/>
+      <c r="J153" s="10"/>
+      <c r="K153" s="10"/>
+      <c r="L153" s="10"/>
+      <c r="M153" s="10"/>
+      <c r="N153" s="10"/>
+    </row>
+    <row r="154" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="10"/>
+      <c r="B154" s="10"/>
+      <c r="C154" s="10"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
+      <c r="G154" s="10"/>
+      <c r="H154" s="10"/>
+      <c r="I154" s="10"/>
+      <c r="J154" s="10"/>
+      <c r="K154" s="10"/>
+      <c r="L154" s="10"/>
+      <c r="M154" s="10"/>
+      <c r="N154" s="10"/>
+    </row>
+    <row r="155" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="10"/>
+      <c r="B155" s="10"/>
+      <c r="C155" s="10"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
+      <c r="H155" s="10"/>
+      <c r="I155" s="10"/>
+      <c r="J155" s="10"/>
+      <c r="K155" s="10"/>
+      <c r="L155" s="10"/>
+      <c r="M155" s="10"/>
+      <c r="N155" s="10"/>
+    </row>
+    <row r="156" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
+      <c r="G156" s="10"/>
+      <c r="H156" s="10"/>
+      <c r="I156" s="10"/>
+      <c r="J156" s="10"/>
+      <c r="K156" s="10"/>
+      <c r="L156" s="10"/>
+      <c r="M156" s="10"/>
+      <c r="N156" s="10"/>
+    </row>
+    <row r="157" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="10"/>
+      <c r="B157" s="10"/>
+      <c r="C157" s="10"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="10"/>
+      <c r="F157" s="10"/>
+      <c r="G157" s="10"/>
+      <c r="H157" s="10"/>
+      <c r="I157" s="10"/>
+      <c r="J157" s="10"/>
+      <c r="K157" s="10"/>
+      <c r="L157" s="10"/>
+      <c r="M157" s="10"/>
+      <c r="N157" s="10"/>
+    </row>
+    <row r="158" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="10"/>
+      <c r="B158" s="10"/>
+      <c r="C158" s="10"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="10"/>
+      <c r="F158" s="10"/>
+      <c r="G158" s="10"/>
+      <c r="H158" s="10"/>
+      <c r="I158" s="10"/>
+      <c r="J158" s="10"/>
+      <c r="K158" s="10"/>
+      <c r="L158" s="10"/>
+      <c r="M158" s="10"/>
+      <c r="N158" s="10"/>
+    </row>
+    <row r="159" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="10"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="10"/>
+      <c r="F159" s="10"/>
+      <c r="G159" s="10"/>
+      <c r="H159" s="10"/>
+      <c r="I159" s="10"/>
+      <c r="J159" s="10"/>
+      <c r="K159" s="10"/>
+      <c r="L159" s="10"/>
+      <c r="M159" s="10"/>
+      <c r="N159" s="10"/>
+    </row>
+    <row r="160" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+      <c r="H160" s="10"/>
+      <c r="I160" s="10"/>
+      <c r="J160" s="10"/>
+      <c r="K160" s="10"/>
+      <c r="L160" s="10"/>
+      <c r="M160" s="10"/>
+      <c r="N160" s="10"/>
+    </row>
+    <row r="161" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="10"/>
+      <c r="B161" s="10"/>
+      <c r="C161" s="10"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="10"/>
+      <c r="F161" s="10"/>
+      <c r="G161" s="10"/>
+      <c r="H161" s="10"/>
+      <c r="I161" s="10"/>
+      <c r="J161" s="10"/>
+      <c r="K161" s="10"/>
+      <c r="L161" s="10"/>
+      <c r="M161" s="10"/>
+      <c r="N161" s="10"/>
+    </row>
+    <row r="162" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="10"/>
+      <c r="B162" s="10"/>
+      <c r="C162" s="10"/>
+      <c r="D162" s="10"/>
+      <c r="E162" s="10"/>
+      <c r="F162" s="10"/>
+      <c r="G162" s="10"/>
+      <c r="H162" s="10"/>
+      <c r="I162" s="10"/>
+      <c r="J162" s="10"/>
+      <c r="K162" s="10"/>
+      <c r="L162" s="10"/>
+      <c r="M162" s="10"/>
+      <c r="N162" s="10"/>
+    </row>
+    <row r="163" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="10"/>
+      <c r="B163" s="10"/>
+      <c r="C163" s="10"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="10"/>
+      <c r="F163" s="10"/>
+      <c r="G163" s="10"/>
+      <c r="H163" s="10"/>
+      <c r="I163" s="10"/>
+      <c r="J163" s="10"/>
+      <c r="K163" s="10"/>
+      <c r="L163" s="10"/>
+      <c r="M163" s="10"/>
+      <c r="N163" s="10"/>
+    </row>
+    <row r="164" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="10"/>
+      <c r="B164" s="10"/>
+      <c r="C164" s="10"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="10"/>
+      <c r="F164" s="10"/>
+      <c r="G164" s="10"/>
+      <c r="H164" s="10"/>
+      <c r="I164" s="10"/>
+      <c r="J164" s="10"/>
+      <c r="K164" s="10"/>
+      <c r="L164" s="10"/>
+      <c r="M164" s="10"/>
+      <c r="N164" s="10"/>
+    </row>
+    <row r="165" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="10"/>
+      <c r="B165" s="10"/>
+      <c r="C165" s="10"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="10"/>
+      <c r="F165" s="10"/>
+      <c r="G165" s="10"/>
+      <c r="H165" s="10"/>
+      <c r="I165" s="10"/>
+      <c r="J165" s="10"/>
+      <c r="K165" s="10"/>
+      <c r="L165" s="10"/>
+      <c r="M165" s="10"/>
+      <c r="N165" s="10"/>
+    </row>
+    <row r="166" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="10"/>
+      <c r="B166" s="10"/>
+      <c r="C166" s="10"/>
+      <c r="D166" s="10"/>
+      <c r="E166" s="10"/>
+      <c r="F166" s="10"/>
+      <c r="G166" s="10"/>
+      <c r="H166" s="10"/>
+      <c r="I166" s="10"/>
+      <c r="J166" s="10"/>
+      <c r="K166" s="10"/>
+      <c r="L166" s="10"/>
+      <c r="M166" s="10"/>
+      <c r="N166" s="10"/>
+    </row>
+    <row r="167" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="10"/>
+      <c r="B167" s="10"/>
+      <c r="C167" s="10"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="10"/>
+      <c r="F167" s="10"/>
+      <c r="G167" s="10"/>
+      <c r="H167" s="10"/>
+      <c r="I167" s="10"/>
+      <c r="J167" s="10"/>
+      <c r="K167" s="10"/>
+      <c r="L167" s="10"/>
+      <c r="M167" s="10"/>
+      <c r="N167" s="10"/>
+    </row>
+    <row r="168" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="10"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="10"/>
+      <c r="D168" s="10"/>
+      <c r="E168" s="10"/>
+      <c r="F168" s="10"/>
+      <c r="G168" s="10"/>
+      <c r="H168" s="10"/>
+      <c r="I168" s="10"/>
+      <c r="J168" s="10"/>
+      <c r="K168" s="10"/>
+      <c r="L168" s="10"/>
+      <c r="M168" s="10"/>
+      <c r="N168" s="10"/>
+    </row>
+    <row r="169" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="10"/>
+      <c r="G169" s="10"/>
+      <c r="H169" s="10"/>
+      <c r="I169" s="10"/>
+      <c r="J169" s="10"/>
+      <c r="K169" s="10"/>
+      <c r="L169" s="10"/>
+      <c r="M169" s="10"/>
+      <c r="N169" s="10"/>
+    </row>
+    <row r="170" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="10"/>
+      <c r="B170" s="10"/>
+      <c r="C170" s="10"/>
+      <c r="D170" s="10"/>
+      <c r="E170" s="10"/>
+      <c r="F170" s="10"/>
+      <c r="G170" s="10"/>
+      <c r="H170" s="10"/>
+      <c r="I170" s="10"/>
+      <c r="J170" s="10"/>
+      <c r="K170" s="10"/>
+      <c r="L170" s="10"/>
+      <c r="M170" s="10"/>
+      <c r="N170" s="10"/>
+    </row>
+    <row r="171" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="10"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="10"/>
+      <c r="F171" s="10"/>
+      <c r="G171" s="10"/>
+      <c r="H171" s="10"/>
+      <c r="I171" s="10"/>
+      <c r="J171" s="10"/>
+      <c r="K171" s="10"/>
+      <c r="L171" s="10"/>
+      <c r="M171" s="10"/>
+      <c r="N171" s="10"/>
+    </row>
+    <row r="172" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="10"/>
+      <c r="B172" s="10"/>
+      <c r="C172" s="10"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="10"/>
+      <c r="G172" s="10"/>
+      <c r="H172" s="10"/>
+      <c r="I172" s="10"/>
+      <c r="J172" s="10"/>
+      <c r="K172" s="10"/>
+      <c r="L172" s="10"/>
+      <c r="M172" s="10"/>
+      <c r="N172" s="10"/>
+    </row>
+    <row r="173" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="10"/>
+      <c r="B173" s="10"/>
+      <c r="C173" s="10"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="10"/>
+      <c r="G173" s="10"/>
+      <c r="H173" s="10"/>
+      <c r="I173" s="10"/>
+      <c r="J173" s="10"/>
+      <c r="K173" s="10"/>
+      <c r="L173" s="10"/>
+      <c r="M173" s="10"/>
+      <c r="N173" s="10"/>
+    </row>
+    <row r="174" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="10"/>
+      <c r="B174" s="10"/>
+      <c r="C174" s="10"/>
+      <c r="D174" s="10"/>
+      <c r="E174" s="10"/>
+      <c r="F174" s="10"/>
+      <c r="G174" s="10"/>
+      <c r="H174" s="10"/>
+      <c r="I174" s="10"/>
+      <c r="J174" s="10"/>
+      <c r="K174" s="10"/>
+      <c r="L174" s="10"/>
+      <c r="M174" s="10"/>
+      <c r="N174" s="10"/>
+    </row>
+    <row r="175" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="10"/>
+      <c r="B175" s="10"/>
+      <c r="C175" s="10"/>
+      <c r="D175" s="10"/>
+      <c r="E175" s="10"/>
+      <c r="F175" s="10"/>
+      <c r="G175" s="10"/>
+      <c r="H175" s="10"/>
+      <c r="I175" s="10"/>
+      <c r="J175" s="10"/>
+      <c r="K175" s="10"/>
+      <c r="L175" s="10"/>
+      <c r="M175" s="10"/>
+      <c r="N175" s="10"/>
+    </row>
+    <row r="176" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="10"/>
+      <c r="B176" s="10"/>
+      <c r="C176" s="10"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="10"/>
+      <c r="F176" s="10"/>
+      <c r="G176" s="10"/>
+      <c r="H176" s="10"/>
+      <c r="I176" s="10"/>
+      <c r="J176" s="10"/>
+      <c r="K176" s="10"/>
+      <c r="L176" s="10"/>
+      <c r="M176" s="10"/>
+      <c r="N176" s="10"/>
+    </row>
+    <row r="177" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="10"/>
+      <c r="B177" s="10"/>
+      <c r="C177" s="10"/>
+      <c r="D177" s="10"/>
+      <c r="E177" s="10"/>
+      <c r="F177" s="10"/>
+      <c r="G177" s="10"/>
+      <c r="H177" s="10"/>
+      <c r="I177" s="10"/>
+      <c r="J177" s="10"/>
+      <c r="K177" s="10"/>
+      <c r="L177" s="10"/>
+      <c r="M177" s="10"/>
+      <c r="N177" s="10"/>
+    </row>
+    <row r="178" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="10"/>
+      <c r="B178" s="10"/>
+      <c r="C178" s="10"/>
+      <c r="D178" s="10"/>
+      <c r="E178" s="10"/>
+      <c r="F178" s="10"/>
+      <c r="G178" s="10"/>
+      <c r="H178" s="10"/>
+      <c r="I178" s="10"/>
+      <c r="J178" s="10"/>
+      <c r="K178" s="10"/>
+      <c r="L178" s="10"/>
+      <c r="M178" s="10"/>
+      <c r="N178" s="10"/>
+    </row>
+    <row r="179" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="10"/>
+      <c r="B179" s="10"/>
+      <c r="C179" s="10"/>
+      <c r="D179" s="10"/>
+      <c r="E179" s="10"/>
+      <c r="F179" s="10"/>
+      <c r="G179" s="10"/>
+      <c r="H179" s="10"/>
+      <c r="I179" s="10"/>
+      <c r="J179" s="10"/>
+      <c r="K179" s="10"/>
+      <c r="L179" s="10"/>
+      <c r="M179" s="10"/>
+      <c r="N179" s="10"/>
+    </row>
+    <row r="180" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="10"/>
+      <c r="B180" s="10"/>
+      <c r="C180" s="10"/>
+      <c r="D180" s="10"/>
+      <c r="E180" s="10"/>
+      <c r="F180" s="10"/>
+      <c r="G180" s="10"/>
+      <c r="H180" s="10"/>
+      <c r="I180" s="10"/>
+      <c r="J180" s="10"/>
+      <c r="K180" s="10"/>
+      <c r="L180" s="10"/>
+      <c r="M180" s="10"/>
+      <c r="N180" s="10"/>
+    </row>
+    <row r="181" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="10"/>
+      <c r="B181" s="10"/>
+      <c r="C181" s="10"/>
+      <c r="D181" s="10"/>
+      <c r="E181" s="10"/>
+      <c r="F181" s="10"/>
+      <c r="G181" s="10"/>
+      <c r="H181" s="10"/>
+      <c r="I181" s="10"/>
+      <c r="J181" s="10"/>
+      <c r="K181" s="10"/>
+      <c r="L181" s="10"/>
+      <c r="M181" s="10"/>
+      <c r="N181" s="10"/>
+    </row>
+    <row r="182" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="10"/>
+      <c r="D182" s="10"/>
+      <c r="E182" s="10"/>
+      <c r="F182" s="10"/>
+      <c r="G182" s="10"/>
+      <c r="H182" s="10"/>
+      <c r="I182" s="10"/>
+      <c r="J182" s="10"/>
+      <c r="K182" s="10"/>
+      <c r="L182" s="10"/>
+      <c r="M182" s="10"/>
+      <c r="N182" s="10"/>
+    </row>
+    <row r="183" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="10"/>
+      <c r="D183" s="10"/>
+      <c r="E183" s="10"/>
+      <c r="F183" s="10"/>
+      <c r="G183" s="10"/>
+      <c r="H183" s="10"/>
+      <c r="I183" s="10"/>
+      <c r="J183" s="10"/>
+      <c r="K183" s="10"/>
+      <c r="L183" s="10"/>
+      <c r="M183" s="10"/>
+      <c r="N183" s="10"/>
+    </row>
+    <row r="184" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="10"/>
+      <c r="B184" s="10"/>
+      <c r="C184" s="10"/>
+      <c r="D184" s="10"/>
+      <c r="E184" s="10"/>
+      <c r="F184" s="10"/>
+      <c r="G184" s="10"/>
+      <c r="H184" s="10"/>
+      <c r="I184" s="10"/>
+      <c r="J184" s="10"/>
+      <c r="K184" s="10"/>
+      <c r="L184" s="10"/>
+      <c r="M184" s="10"/>
+      <c r="N184" s="10"/>
+    </row>
+    <row r="185" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="10"/>
+      <c r="B185" s="10"/>
+      <c r="C185" s="10"/>
+      <c r="D185" s="10"/>
+      <c r="E185" s="10"/>
+      <c r="F185" s="10"/>
+      <c r="G185" s="10"/>
+      <c r="H185" s="10"/>
+      <c r="I185" s="10"/>
+      <c r="J185" s="10"/>
+      <c r="K185" s="10"/>
+      <c r="L185" s="10"/>
+      <c r="M185" s="10"/>
+      <c r="N185" s="10"/>
+    </row>
+    <row r="186" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="10"/>
+      <c r="B186" s="10"/>
+      <c r="C186" s="10"/>
+      <c r="D186" s="10"/>
+      <c r="E186" s="10"/>
+      <c r="F186" s="10"/>
+      <c r="G186" s="10"/>
+      <c r="H186" s="10"/>
+      <c r="I186" s="10"/>
+      <c r="J186" s="10"/>
+      <c r="K186" s="10"/>
+      <c r="L186" s="10"/>
+      <c r="M186" s="10"/>
+      <c r="N186" s="10"/>
+    </row>
+    <row r="187" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="10"/>
+      <c r="B187" s="10"/>
+      <c r="C187" s="10"/>
+      <c r="D187" s="10"/>
+      <c r="E187" s="10"/>
+      <c r="F187" s="10"/>
+      <c r="G187" s="10"/>
+      <c r="H187" s="10"/>
+      <c r="I187" s="10"/>
+      <c r="J187" s="10"/>
+      <c r="K187" s="10"/>
+      <c r="L187" s="10"/>
+      <c r="M187" s="10"/>
+      <c r="N187" s="10"/>
+    </row>
+    <row r="188" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="10"/>
+      <c r="B188" s="10"/>
+      <c r="C188" s="10"/>
+      <c r="D188" s="10"/>
+      <c r="E188" s="10"/>
+      <c r="F188" s="10"/>
+      <c r="G188" s="10"/>
+      <c r="H188" s="10"/>
+      <c r="I188" s="10"/>
+      <c r="J188" s="10"/>
+      <c r="K188" s="10"/>
+      <c r="L188" s="10"/>
+      <c r="M188" s="10"/>
+      <c r="N188" s="10"/>
+    </row>
+    <row r="189" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="10"/>
+      <c r="B189" s="10"/>
+      <c r="C189" s="10"/>
+      <c r="D189" s="10"/>
+      <c r="E189" s="10"/>
+      <c r="F189" s="10"/>
+      <c r="G189" s="10"/>
+      <c r="H189" s="10"/>
+      <c r="I189" s="10"/>
+      <c r="J189" s="10"/>
+      <c r="K189" s="10"/>
+      <c r="L189" s="10"/>
+      <c r="M189" s="10"/>
+      <c r="N189" s="10"/>
+    </row>
+    <row r="190" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="10"/>
+      <c r="B190" s="10"/>
+      <c r="C190" s="10"/>
+      <c r="D190" s="10"/>
+      <c r="E190" s="10"/>
+      <c r="F190" s="10"/>
+      <c r="G190" s="10"/>
+      <c r="H190" s="10"/>
+      <c r="I190" s="10"/>
+      <c r="J190" s="10"/>
+      <c r="K190" s="10"/>
+      <c r="L190" s="10"/>
+      <c r="M190" s="10"/>
+      <c r="N190" s="10"/>
+    </row>
+    <row r="191" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="10"/>
+      <c r="B191" s="10"/>
+      <c r="C191" s="10"/>
+      <c r="D191" s="10"/>
+      <c r="E191" s="10"/>
+      <c r="F191" s="10"/>
+      <c r="G191" s="10"/>
+      <c r="H191" s="10"/>
+      <c r="I191" s="10"/>
+      <c r="J191" s="10"/>
+      <c r="K191" s="10"/>
+      <c r="L191" s="10"/>
+      <c r="M191" s="10"/>
+      <c r="N191" s="10"/>
+    </row>
+    <row r="192" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="10"/>
+      <c r="B192" s="10"/>
+      <c r="C192" s="10"/>
+      <c r="D192" s="10"/>
+      <c r="E192" s="10"/>
+      <c r="F192" s="10"/>
+      <c r="G192" s="10"/>
+      <c r="H192" s="10"/>
+      <c r="I192" s="10"/>
+      <c r="J192" s="10"/>
+      <c r="K192" s="10"/>
+      <c r="L192" s="10"/>
+      <c r="M192" s="10"/>
+      <c r="N192" s="10"/>
+    </row>
+    <row r="193" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="10"/>
+      <c r="B193" s="10"/>
+      <c r="C193" s="10"/>
+      <c r="D193" s="10"/>
+      <c r="E193" s="10"/>
+      <c r="F193" s="10"/>
+      <c r="G193" s="10"/>
+      <c r="H193" s="10"/>
+      <c r="I193" s="10"/>
+      <c r="J193" s="10"/>
+      <c r="K193" s="10"/>
+      <c r="L193" s="10"/>
+      <c r="M193" s="10"/>
+      <c r="N193" s="10"/>
+    </row>
+    <row r="194" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="10"/>
+      <c r="B194" s="10"/>
+      <c r="C194" s="10"/>
+      <c r="D194" s="10"/>
+      <c r="E194" s="10"/>
+      <c r="F194" s="10"/>
+      <c r="G194" s="10"/>
+      <c r="H194" s="10"/>
+      <c r="I194" s="10"/>
+      <c r="J194" s="10"/>
+      <c r="K194" s="10"/>
+      <c r="L194" s="10"/>
+      <c r="M194" s="10"/>
+      <c r="N194" s="10"/>
+    </row>
+    <row r="195" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="10"/>
+      <c r="B195" s="10"/>
+      <c r="C195" s="10"/>
+      <c r="D195" s="10"/>
+      <c r="E195" s="10"/>
+      <c r="F195" s="10"/>
+      <c r="G195" s="10"/>
+      <c r="H195" s="10"/>
+      <c r="I195" s="10"/>
+      <c r="J195" s="10"/>
+      <c r="K195" s="10"/>
+      <c r="L195" s="10"/>
+      <c r="M195" s="10"/>
+      <c r="N195" s="10"/>
+    </row>
+    <row r="196" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="10"/>
+      <c r="B196" s="10"/>
+      <c r="C196" s="10"/>
+      <c r="D196" s="10"/>
+      <c r="E196" s="10"/>
+      <c r="F196" s="10"/>
+      <c r="G196" s="10"/>
+      <c r="H196" s="10"/>
+      <c r="I196" s="10"/>
+      <c r="J196" s="10"/>
+      <c r="K196" s="10"/>
+      <c r="L196" s="10"/>
+      <c r="M196" s="10"/>
+      <c r="N196" s="10"/>
+    </row>
+    <row r="197" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="10"/>
+      <c r="B197" s="10"/>
+      <c r="C197" s="10"/>
+      <c r="D197" s="10"/>
+      <c r="E197" s="10"/>
+      <c r="F197" s="10"/>
+      <c r="G197" s="10"/>
+      <c r="H197" s="10"/>
+      <c r="I197" s="10"/>
+      <c r="J197" s="10"/>
+      <c r="K197" s="10"/>
+      <c r="L197" s="10"/>
+      <c r="M197" s="10"/>
+      <c r="N197" s="10"/>
+    </row>
+    <row r="198" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="10"/>
+      <c r="B198" s="10"/>
+      <c r="C198" s="10"/>
+      <c r="D198" s="10"/>
+      <c r="E198" s="10"/>
+      <c r="F198" s="10"/>
+      <c r="G198" s="10"/>
+      <c r="H198" s="10"/>
+      <c r="I198" s="10"/>
+      <c r="J198" s="10"/>
+      <c r="K198" s="10"/>
+      <c r="L198" s="10"/>
+      <c r="M198" s="10"/>
+      <c r="N198" s="10"/>
+    </row>
+    <row r="199" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="10"/>
+      <c r="B199" s="10"/>
+      <c r="C199" s="10"/>
+      <c r="D199" s="10"/>
+      <c r="E199" s="10"/>
+      <c r="F199" s="10"/>
+      <c r="G199" s="10"/>
+      <c r="H199" s="10"/>
+      <c r="I199" s="10"/>
+      <c r="J199" s="10"/>
+      <c r="K199" s="10"/>
+      <c r="L199" s="10"/>
+      <c r="M199" s="10"/>
+      <c r="N199" s="10"/>
+    </row>
+    <row r="200" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="10"/>
+      <c r="B200" s="10"/>
+      <c r="C200" s="10"/>
+      <c r="D200" s="10"/>
+      <c r="E200" s="10"/>
+      <c r="F200" s="10"/>
+      <c r="G200" s="10"/>
+      <c r="H200" s="10"/>
+      <c r="I200" s="10"/>
+      <c r="J200" s="10"/>
+      <c r="K200" s="10"/>
+      <c r="L200" s="10"/>
+      <c r="M200" s="10"/>
+      <c r="N200" s="10"/>
+    </row>
+    <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="10"/>
+      <c r="B201" s="10"/>
+      <c r="C201" s="10"/>
+      <c r="D201" s="10"/>
+      <c r="E201" s="10"/>
+      <c r="F201" s="10"/>
+      <c r="G201" s="10"/>
+      <c r="H201" s="10"/>
+      <c r="I201" s="10"/>
+      <c r="J201" s="10"/>
+      <c r="K201" s="10"/>
+      <c r="L201" s="10"/>
+      <c r="M201" s="10"/>
+      <c r="N201" s="10"/>
+    </row>
+    <row r="202" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="10"/>
+      <c r="B202" s="10"/>
+      <c r="C202" s="10"/>
+      <c r="D202" s="10"/>
+      <c r="E202" s="10"/>
+      <c r="F202" s="10"/>
+      <c r="G202" s="10"/>
+      <c r="H202" s="10"/>
+      <c r="I202" s="10"/>
+      <c r="J202" s="10"/>
+      <c r="K202" s="10"/>
+      <c r="L202" s="10"/>
+      <c r="M202" s="10"/>
+      <c r="N202" s="10"/>
+    </row>
+    <row r="203" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="10"/>
+      <c r="B203" s="10"/>
+      <c r="C203" s="10"/>
+      <c r="D203" s="10"/>
+      <c r="E203" s="10"/>
+      <c r="F203" s="10"/>
+      <c r="G203" s="10"/>
+      <c r="H203" s="10"/>
+      <c r="I203" s="10"/>
+      <c r="J203" s="10"/>
+      <c r="K203" s="10"/>
+      <c r="L203" s="10"/>
+      <c r="M203" s="10"/>
+      <c r="N203" s="10"/>
+    </row>
+    <row r="204" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="10"/>
+      <c r="B204" s="10"/>
+      <c r="C204" s="10"/>
+      <c r="D204" s="10"/>
+      <c r="E204" s="10"/>
+      <c r="F204" s="10"/>
+      <c r="G204" s="10"/>
+      <c r="H204" s="10"/>
+      <c r="I204" s="10"/>
+      <c r="J204" s="10"/>
+      <c r="K204" s="10"/>
+      <c r="L204" s="10"/>
+      <c r="M204" s="10"/>
+      <c r="N204" s="10"/>
+    </row>
+    <row r="205" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="10"/>
+      <c r="B205" s="10"/>
+      <c r="C205" s="10"/>
+      <c r="D205" s="10"/>
+      <c r="E205" s="10"/>
+      <c r="F205" s="10"/>
+      <c r="G205" s="10"/>
+      <c r="H205" s="10"/>
+      <c r="I205" s="10"/>
+      <c r="J205" s="10"/>
+      <c r="K205" s="10"/>
+      <c r="L205" s="10"/>
+      <c r="M205" s="10"/>
+      <c r="N205" s="10"/>
+    </row>
+    <row r="206" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="10"/>
+      <c r="B206" s="10"/>
+      <c r="C206" s="10"/>
+      <c r="D206" s="10"/>
+      <c r="E206" s="10"/>
+      <c r="F206" s="10"/>
+      <c r="G206" s="10"/>
+      <c r="H206" s="10"/>
+      <c r="I206" s="10"/>
+      <c r="J206" s="10"/>
+      <c r="K206" s="10"/>
+      <c r="L206" s="10"/>
+      <c r="M206" s="10"/>
+      <c r="N206" s="10"/>
+    </row>
+    <row r="207" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="10"/>
+      <c r="B207" s="10"/>
+      <c r="C207" s="10"/>
+      <c r="D207" s="10"/>
+      <c r="E207" s="10"/>
+      <c r="F207" s="10"/>
+      <c r="G207" s="10"/>
+      <c r="H207" s="10"/>
+      <c r="I207" s="10"/>
+      <c r="J207" s="10"/>
+      <c r="K207" s="10"/>
+      <c r="L207" s="10"/>
+      <c r="M207" s="10"/>
+      <c r="N207" s="10"/>
+    </row>
+    <row r="208" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="10"/>
+      <c r="B208" s="10"/>
+      <c r="C208" s="10"/>
+      <c r="D208" s="10"/>
+      <c r="E208" s="10"/>
+      <c r="F208" s="10"/>
+      <c r="G208" s="10"/>
+      <c r="H208" s="10"/>
+      <c r="I208" s="10"/>
+      <c r="J208" s="10"/>
+      <c r="K208" s="10"/>
+      <c r="L208" s="10"/>
+      <c r="M208" s="10"/>
+      <c r="N208" s="10"/>
+    </row>
+    <row r="209" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="10"/>
+      <c r="B209" s="10"/>
+      <c r="C209" s="10"/>
+      <c r="D209" s="10"/>
+      <c r="E209" s="10"/>
+      <c r="F209" s="10"/>
+      <c r="G209" s="10"/>
+      <c r="H209" s="10"/>
+      <c r="I209" s="10"/>
+      <c r="J209" s="10"/>
+      <c r="K209" s="10"/>
+      <c r="L209" s="10"/>
+      <c r="M209" s="10"/>
+      <c r="N209" s="10"/>
+    </row>
+    <row r="210" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="10"/>
+      <c r="B210" s="10"/>
+      <c r="C210" s="10"/>
+      <c r="D210" s="10"/>
+      <c r="E210" s="10"/>
+      <c r="F210" s="10"/>
+      <c r="G210" s="10"/>
+      <c r="H210" s="10"/>
+      <c r="I210" s="10"/>
+      <c r="J210" s="10"/>
+      <c r="K210" s="10"/>
+      <c r="L210" s="10"/>
+      <c r="M210" s="10"/>
+      <c r="N210" s="10"/>
+    </row>
+    <row r="211" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="10"/>
+      <c r="B211" s="10"/>
+      <c r="C211" s="10"/>
+      <c r="D211" s="10"/>
+      <c r="E211" s="10"/>
+      <c r="F211" s="10"/>
+      <c r="G211" s="10"/>
+      <c r="H211" s="10"/>
+      <c r="I211" s="10"/>
+      <c r="J211" s="10"/>
+      <c r="K211" s="10"/>
+      <c r="L211" s="10"/>
+      <c r="M211" s="10"/>
+      <c r="N211" s="10"/>
+    </row>
+    <row r="212" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="10"/>
+      <c r="B212" s="10"/>
+      <c r="C212" s="10"/>
+      <c r="D212" s="10"/>
+      <c r="E212" s="10"/>
+      <c r="F212" s="10"/>
+      <c r="G212" s="10"/>
+      <c r="H212" s="10"/>
+      <c r="I212" s="10"/>
+      <c r="J212" s="10"/>
+      <c r="K212" s="10"/>
+      <c r="L212" s="10"/>
+      <c r="M212" s="10"/>
+      <c r="N212" s="10"/>
+    </row>
+    <row r="213" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="10"/>
+      <c r="B213" s="10"/>
+      <c r="C213" s="10"/>
+      <c r="D213" s="10"/>
+      <c r="E213" s="10"/>
+      <c r="F213" s="10"/>
+      <c r="G213" s="10"/>
+      <c r="H213" s="10"/>
+      <c r="I213" s="10"/>
+      <c r="J213" s="10"/>
+      <c r="K213" s="10"/>
+      <c r="L213" s="10"/>
+      <c r="M213" s="10"/>
+      <c r="N213" s="10"/>
+    </row>
+    <row r="214" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="10"/>
+      <c r="B214" s="10"/>
+      <c r="C214" s="10"/>
+      <c r="D214" s="10"/>
+      <c r="E214" s="10"/>
+      <c r="F214" s="10"/>
+      <c r="G214" s="10"/>
+      <c r="H214" s="10"/>
+      <c r="I214" s="10"/>
+      <c r="J214" s="10"/>
+      <c r="K214" s="10"/>
+      <c r="L214" s="10"/>
+      <c r="M214" s="10"/>
+      <c r="N214" s="10"/>
+    </row>
+    <row r="215" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="10"/>
+      <c r="B215" s="10"/>
+      <c r="C215" s="10"/>
+      <c r="D215" s="10"/>
+      <c r="E215" s="10"/>
+      <c r="F215" s="10"/>
+      <c r="G215" s="10"/>
+      <c r="H215" s="10"/>
+      <c r="I215" s="10"/>
+      <c r="J215" s="10"/>
+      <c r="K215" s="10"/>
+      <c r="L215" s="10"/>
+      <c r="M215" s="10"/>
+      <c r="N215" s="10"/>
+    </row>
+    <row r="216" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="10"/>
+      <c r="B216" s="10"/>
+      <c r="C216" s="10"/>
+      <c r="D216" s="10"/>
+      <c r="E216" s="10"/>
+      <c r="F216" s="10"/>
+      <c r="G216" s="10"/>
+      <c r="H216" s="10"/>
+      <c r="I216" s="10"/>
+      <c r="J216" s="10"/>
+      <c r="K216" s="10"/>
+      <c r="L216" s="10"/>
+      <c r="M216" s="10"/>
+      <c r="N216" s="10"/>
+    </row>
+    <row r="217" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="10"/>
+      <c r="B217" s="10"/>
+      <c r="C217" s="10"/>
+      <c r="D217" s="10"/>
+      <c r="E217" s="10"/>
+      <c r="F217" s="10"/>
+      <c r="G217" s="10"/>
+      <c r="H217" s="10"/>
+      <c r="I217" s="10"/>
+      <c r="J217" s="10"/>
+      <c r="K217" s="10"/>
+      <c r="L217" s="10"/>
+      <c r="M217" s="10"/>
+      <c r="N217" s="10"/>
+    </row>
+    <row r="218" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="10"/>
+      <c r="B218" s="10"/>
+      <c r="C218" s="10"/>
+      <c r="D218" s="10"/>
+      <c r="E218" s="10"/>
+      <c r="F218" s="10"/>
+      <c r="G218" s="10"/>
+      <c r="H218" s="10"/>
+      <c r="I218" s="10"/>
+      <c r="J218" s="10"/>
+      <c r="K218" s="10"/>
+      <c r="L218" s="10"/>
+      <c r="M218" s="10"/>
+      <c r="N218" s="10"/>
+    </row>
+    <row r="219" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="10"/>
+      <c r="B219" s="10"/>
+      <c r="C219" s="10"/>
+      <c r="D219" s="10"/>
+      <c r="E219" s="10"/>
+      <c r="F219" s="10"/>
+      <c r="G219" s="10"/>
+      <c r="H219" s="10"/>
+      <c r="I219" s="10"/>
+      <c r="J219" s="10"/>
+      <c r="K219" s="10"/>
+      <c r="L219" s="10"/>
+      <c r="M219" s="10"/>
+      <c r="N219" s="10"/>
+    </row>
+    <row r="220" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="10"/>
+      <c r="B220" s="10"/>
+      <c r="C220" s="10"/>
+      <c r="D220" s="10"/>
+      <c r="E220" s="10"/>
+      <c r="F220" s="10"/>
+      <c r="G220" s="10"/>
+      <c r="H220" s="10"/>
+      <c r="I220" s="10"/>
+      <c r="J220" s="10"/>
+      <c r="K220" s="10"/>
+      <c r="L220" s="10"/>
+      <c r="M220" s="10"/>
+      <c r="N220" s="10"/>
+    </row>
+    <row r="221" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="10"/>
+      <c r="B221" s="10"/>
+      <c r="C221" s="10"/>
+      <c r="D221" s="10"/>
+      <c r="E221" s="10"/>
+      <c r="F221" s="10"/>
+      <c r="G221" s="10"/>
+      <c r="H221" s="10"/>
+      <c r="I221" s="10"/>
+      <c r="J221" s="10"/>
+      <c r="K221" s="10"/>
+      <c r="L221" s="10"/>
+      <c r="M221" s="10"/>
+      <c r="N221" s="10"/>
+    </row>
+    <row r="222" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="10"/>
+      <c r="B222" s="10"/>
+      <c r="C222" s="10"/>
+      <c r="D222" s="10"/>
+      <c r="E222" s="10"/>
+      <c r="F222" s="10"/>
+      <c r="G222" s="10"/>
+      <c r="H222" s="10"/>
+      <c r="I222" s="10"/>
+      <c r="J222" s="10"/>
+      <c r="K222" s="10"/>
+      <c r="L222" s="10"/>
+      <c r="M222" s="10"/>
+      <c r="N222" s="10"/>
+    </row>
+    <row r="223" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="10"/>
+      <c r="B223" s="10"/>
+      <c r="C223" s="10"/>
+      <c r="D223" s="10"/>
+      <c r="E223" s="10"/>
+      <c r="F223" s="10"/>
+      <c r="G223" s="10"/>
+      <c r="H223" s="10"/>
+      <c r="I223" s="10"/>
+      <c r="J223" s="10"/>
+      <c r="K223" s="10"/>
+      <c r="L223" s="10"/>
+      <c r="M223" s="10"/>
+      <c r="N223" s="10"/>
+    </row>
+    <row r="224" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="10"/>
+      <c r="B224" s="10"/>
+      <c r="C224" s="10"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="10"/>
+      <c r="F224" s="10"/>
+      <c r="G224" s="10"/>
+      <c r="H224" s="10"/>
+      <c r="I224" s="10"/>
+      <c r="J224" s="10"/>
+      <c r="K224" s="10"/>
+      <c r="L224" s="10"/>
+      <c r="M224" s="10"/>
+      <c r="N224" s="10"/>
+    </row>
+    <row r="225" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="10"/>
+      <c r="B225" s="10"/>
+      <c r="C225" s="10"/>
+      <c r="D225" s="10"/>
+      <c r="E225" s="10"/>
+      <c r="F225" s="10"/>
+      <c r="G225" s="10"/>
+      <c r="H225" s="10"/>
+      <c r="I225" s="10"/>
+      <c r="J225" s="10"/>
+      <c r="K225" s="10"/>
+      <c r="L225" s="10"/>
+      <c r="M225" s="10"/>
+      <c r="N225" s="10"/>
+    </row>
+    <row r="226" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="10"/>
+      <c r="B226" s="10"/>
+      <c r="C226" s="10"/>
+      <c r="D226" s="10"/>
+      <c r="E226" s="10"/>
+      <c r="F226" s="10"/>
+      <c r="G226" s="10"/>
+      <c r="H226" s="10"/>
+      <c r="I226" s="10"/>
+      <c r="J226" s="10"/>
+      <c r="K226" s="10"/>
+      <c r="L226" s="10"/>
+      <c r="M226" s="10"/>
+      <c r="N226" s="10"/>
+    </row>
+    <row r="227" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="10"/>
+      <c r="B227" s="10"/>
+      <c r="C227" s="10"/>
+      <c r="D227" s="10"/>
+      <c r="E227" s="10"/>
+      <c r="F227" s="10"/>
+      <c r="G227" s="10"/>
+      <c r="H227" s="10"/>
+      <c r="I227" s="10"/>
+      <c r="J227" s="10"/>
+      <c r="K227" s="10"/>
+      <c r="L227" s="10"/>
+      <c r="M227" s="10"/>
+      <c r="N227" s="10"/>
+    </row>
+    <row r="228" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="10"/>
+      <c r="B228" s="10"/>
+      <c r="C228" s="10"/>
+      <c r="D228" s="10"/>
+      <c r="E228" s="10"/>
+      <c r="F228" s="10"/>
+      <c r="G228" s="10"/>
+      <c r="H228" s="10"/>
+      <c r="I228" s="10"/>
+      <c r="J228" s="10"/>
+      <c r="K228" s="10"/>
+      <c r="L228" s="10"/>
+      <c r="M228" s="10"/>
+      <c r="N228" s="10"/>
+    </row>
+    <row r="229" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="10"/>
+      <c r="B229" s="10"/>
+      <c r="C229" s="10"/>
+      <c r="D229" s="10"/>
+      <c r="E229" s="10"/>
+      <c r="F229" s="10"/>
+      <c r="G229" s="10"/>
+      <c r="H229" s="10"/>
+      <c r="I229" s="10"/>
+      <c r="J229" s="10"/>
+      <c r="K229" s="10"/>
+      <c r="L229" s="10"/>
+      <c r="M229" s="10"/>
+      <c r="N229" s="10"/>
+    </row>
+    <row r="230" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="10"/>
+      <c r="B230" s="10"/>
+      <c r="C230" s="10"/>
+      <c r="D230" s="10"/>
+      <c r="E230" s="10"/>
+      <c r="F230" s="10"/>
+      <c r="G230" s="10"/>
+      <c r="H230" s="10"/>
+      <c r="I230" s="10"/>
+      <c r="J230" s="10"/>
+      <c r="K230" s="10"/>
+      <c r="L230" s="10"/>
+      <c r="M230" s="10"/>
+      <c r="N230" s="10"/>
+    </row>
+    <row r="231" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="10"/>
+      <c r="B231" s="10"/>
+      <c r="C231" s="10"/>
+      <c r="D231" s="10"/>
+      <c r="E231" s="10"/>
+      <c r="F231" s="10"/>
+      <c r="G231" s="10"/>
+      <c r="H231" s="10"/>
+      <c r="I231" s="10"/>
+      <c r="J231" s="10"/>
+      <c r="K231" s="10"/>
+      <c r="L231" s="10"/>
+      <c r="M231" s="10"/>
+      <c r="N231" s="10"/>
+    </row>
+    <row r="232" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="10"/>
+      <c r="B232" s="10"/>
+      <c r="C232" s="10"/>
+      <c r="D232" s="10"/>
+      <c r="E232" s="10"/>
+      <c r="F232" s="10"/>
+      <c r="G232" s="10"/>
+      <c r="H232" s="10"/>
+      <c r="I232" s="10"/>
+      <c r="J232" s="10"/>
+      <c r="K232" s="10"/>
+      <c r="L232" s="10"/>
+      <c r="M232" s="10"/>
+      <c r="N232" s="10"/>
+    </row>
+    <row r="233" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="10"/>
+      <c r="B233" s="10"/>
+      <c r="C233" s="10"/>
+      <c r="D233" s="10"/>
+      <c r="E233" s="10"/>
+      <c r="F233" s="10"/>
+      <c r="G233" s="10"/>
+      <c r="H233" s="10"/>
+      <c r="I233" s="10"/>
+      <c r="J233" s="10"/>
+      <c r="K233" s="10"/>
+      <c r="L233" s="10"/>
+      <c r="M233" s="10"/>
+      <c r="N233" s="10"/>
+    </row>
+    <row r="234" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="10"/>
+      <c r="B234" s="10"/>
+      <c r="C234" s="10"/>
+      <c r="D234" s="10"/>
+      <c r="E234" s="10"/>
+      <c r="F234" s="10"/>
+      <c r="G234" s="10"/>
+      <c r="H234" s="10"/>
+      <c r="I234" s="10"/>
+      <c r="J234" s="10"/>
+      <c r="K234" s="10"/>
+      <c r="L234" s="10"/>
+      <c r="M234" s="10"/>
+      <c r="N234" s="10"/>
+    </row>
+    <row r="235" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="10"/>
+      <c r="B235" s="10"/>
+      <c r="C235" s="10"/>
+      <c r="D235" s="10"/>
+      <c r="E235" s="10"/>
+      <c r="F235" s="10"/>
+      <c r="G235" s="10"/>
+      <c r="H235" s="10"/>
+      <c r="I235" s="10"/>
+      <c r="J235" s="10"/>
+      <c r="K235" s="10"/>
+      <c r="L235" s="10"/>
+      <c r="M235" s="10"/>
+      <c r="N235" s="10"/>
+    </row>
+    <row r="236" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="10"/>
+      <c r="B236" s="10"/>
+      <c r="C236" s="10"/>
+      <c r="D236" s="10"/>
+      <c r="E236" s="10"/>
+      <c r="F236" s="10"/>
+      <c r="G236" s="10"/>
+      <c r="H236" s="10"/>
+      <c r="I236" s="10"/>
+      <c r="J236" s="10"/>
+      <c r="K236" s="10"/>
+      <c r="L236" s="10"/>
+      <c r="M236" s="10"/>
+      <c r="N236" s="10"/>
+    </row>
+    <row r="237" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="10"/>
+      <c r="B237" s="10"/>
+      <c r="C237" s="10"/>
+      <c r="D237" s="10"/>
+      <c r="E237" s="10"/>
+      <c r="F237" s="10"/>
+      <c r="G237" s="10"/>
+      <c r="H237" s="10"/>
+      <c r="I237" s="10"/>
+      <c r="J237" s="10"/>
+      <c r="K237" s="10"/>
+      <c r="L237" s="10"/>
+      <c r="M237" s="10"/>
+      <c r="N237" s="10"/>
+    </row>
+    <row r="238" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="10"/>
+      <c r="B238" s="10"/>
+      <c r="C238" s="10"/>
+      <c r="D238" s="10"/>
+      <c r="E238" s="10"/>
+      <c r="F238" s="10"/>
+      <c r="G238" s="10"/>
+      <c r="H238" s="10"/>
+      <c r="I238" s="10"/>
+      <c r="J238" s="10"/>
+      <c r="K238" s="10"/>
+      <c r="L238" s="10"/>
+      <c r="M238" s="10"/>
+      <c r="N238" s="10"/>
+    </row>
+    <row r="239" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="10"/>
+      <c r="B239" s="10"/>
+      <c r="C239" s="10"/>
+      <c r="D239" s="10"/>
+      <c r="E239" s="10"/>
+      <c r="F239" s="10"/>
+      <c r="G239" s="10"/>
+      <c r="H239" s="10"/>
+      <c r="I239" s="10"/>
+      <c r="J239" s="10"/>
+      <c r="K239" s="10"/>
+      <c r="L239" s="10"/>
+      <c r="M239" s="10"/>
+      <c r="N239" s="10"/>
+    </row>
+    <row r="240" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="10"/>
+      <c r="B240" s="10"/>
+      <c r="C240" s="10"/>
+      <c r="D240" s="10"/>
+      <c r="E240" s="10"/>
+      <c r="F240" s="10"/>
+      <c r="G240" s="10"/>
+      <c r="H240" s="10"/>
+      <c r="I240" s="10"/>
+      <c r="J240" s="10"/>
+      <c r="K240" s="10"/>
+      <c r="L240" s="10"/>
+      <c r="M240" s="10"/>
+      <c r="N240" s="10"/>
+    </row>
+    <row r="241" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="10"/>
+      <c r="B241" s="10"/>
+      <c r="C241" s="10"/>
+      <c r="D241" s="10"/>
+      <c r="E241" s="10"/>
+      <c r="F241" s="10"/>
+      <c r="G241" s="10"/>
+      <c r="H241" s="10"/>
+      <c r="I241" s="10"/>
+      <c r="J241" s="10"/>
+      <c r="K241" s="10"/>
+      <c r="L241" s="10"/>
+      <c r="M241" s="10"/>
+      <c r="N241" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
